--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_hrp_quarterly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_hrp_quarterly.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -890,12 +890,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -916,77 +916,81 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>10.17834612260288</v>
+        <v>1.665738793173225</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.3108792038122499</v>
+        <v>-0.8356629845388652</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.3830918012000365</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.0830167089904766</v>
+        <v>0.1159165162158591</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.164563240394407</v>
+        <v>0.1110556358720072</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9098267537631355</v>
+        <v>0.8398182334564044</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.09022589446255025</v>
+        <v>0.03570960844154136</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.3974800294591584</v>
+        <v>0.1271002193429802</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.5599655894391498</v>
+        <v>0.1732213886951469</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>0.2455127207029907</v>
+        <v>0.09321423306288697</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.6051970115039702</v>
+        <v>0.9520079944713302</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="X4" s="2" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>-0.1311111803263585</v>
+        <v>-0.7927930833278594</v>
       </c>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
@@ -998,11 +1002,11 @@
         </is>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AH4" s="2" t="n">
@@ -1028,7 +1032,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1059,51 +1063,51 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.665738793173225</v>
+        <v>11.25083731358982</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.8356629845388652</v>
+        <v>-0.244762447779545</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.3830918012000365</v>
+        <v>-0.367499876194607</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1159165162158591</v>
+        <v>0.08326931842306221</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1110556358720072</v>
+        <v>0.1669508898731428</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.8398182334564044</v>
+        <v>0.9017324623686452</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.03570960844154136</v>
+        <v>0.09380606175868089</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.1271002193429802</v>
+        <v>0.4114324850062793</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.1732213886951469</v>
+        <v>0.5794504470198649</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>0.09321423306288697</v>
+        <v>0.2552546758111193</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.9520079944713302</v>
+        <v>0.89672861203617</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="X5" s="2" t="n">
@@ -1115,15 +1119,15 @@
         </is>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>-0.7927930833278594</v>
+        <v>-0.04774682617000037</v>
       </c>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="n">
@@ -1135,11 +1139,11 @@
         </is>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AH5" s="2" t="n">
@@ -1165,7 +1169,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1183,68 +1187,64 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>11.25083731358982</v>
+        <v>4.544418441036771</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.244762447779545</v>
+        <v>-0.6581986271869318</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.367499876194607</v>
+        <v>-0.4201681847926454</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.08326931842306221</v>
+        <v>0.1254210473062694</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1669508898731428</v>
+        <v>0.1384981731821992</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9017324623686452</v>
+        <v>0.9314115308151093</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>0.09380606175868089</v>
+        <v>0.0632101191414598</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.4114324850062793</v>
+        <v>0.2911215893997258</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.5794504470198649</v>
+        <v>0.4029807176230412</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>0.2552546758111193</v>
+        <v>0.1504400414625734</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.89672861203617</v>
+        <v>1.554147077298945</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="X6" s="2" t="n">
@@ -1256,19 +1256,17 @@
         </is>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>-0.04774682617000037</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>0.09594363774604675</v>
-      </c>
+        <v>-0.5690343506837612</v>
+      </c>
+      <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="n">
         <v>0.3333333333333333</v>
       </c>
@@ -1293,30 +1291,12 @@
           <t>0/6</t>
         </is>
       </c>
-      <c r="AJ6" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AL6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AN6" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
+      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" s="2" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" s="2" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1326,7 +1306,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1357,51 +1337,51 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>4.544418441036771</v>
+        <v>10.85389193431626</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.6581986271869318</v>
+        <v>-0.2692332695637203</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.4201681847926454</v>
+        <v>-0.4000942896051514</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1254210473062694</v>
+        <v>0.09172596379613251</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1384981731821992</v>
+        <v>0.1689841665263522</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9314115308151093</v>
+        <v>0.9027264981539336</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.0632101191414598</v>
+        <v>0.09251755508926141</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.2911215893997258</v>
+        <v>0.399507284637408</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.4029807176230412</v>
+        <v>0.5621966199816507</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>0.1504400414625734</v>
+        <v>0.2312393790487886</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>1.554147077298945</v>
+        <v>1.058182916812717</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="X7" s="2" t="n">
@@ -1413,15 +1393,15 @@
         </is>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AB7" s="2" t="n">
-        <v>-0.5690343506837612</v>
+        <v>-0.07860124759237053</v>
       </c>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="n">
@@ -1441,11 +1421,11 @@
         </is>
       </c>
       <c r="AH7" s="2" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr"/>
@@ -1463,7 +1443,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1481,68 +1461,64 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>10.85389193431626</v>
+        <v>2.238641062532729</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.2692332695637203</v>
+        <v>-0.8003448020753167</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.4000942896051514</v>
+        <v>-0.2902464771828116</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.09172596379613251</v>
+        <v>0.0941874374009169</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1689841665263522</v>
+        <v>0.1074695015079701</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9027264981539336</v>
+        <v>0.8729054245952854</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>0.09251755508926141</v>
+        <v>0.04294998108173242</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.399507284637408</v>
+        <v>0.1961608904197224</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.5621966199816507</v>
+        <v>0.2673921090207879</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>0.2312393790487886</v>
+        <v>0.1479776137116744</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>1.058182916812717</v>
+        <v>1.799010124146353</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="X8" s="2" t="n">
@@ -1554,19 +1530,17 @@
         </is>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>-0.07860124759237053</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>0.06043343123428713</v>
-      </c>
+        <v>-0.7482615961872359</v>
+      </c>
+      <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="n">
         <v>0.3333333333333333</v>
       </c>
@@ -1576,45 +1550,27 @@
         </is>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AH8" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AJ8" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AL8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
           <t>0/6</t>
         </is>
       </c>
-      <c r="AN8" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
+      <c r="AJ8" s="2" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" s="2" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" s="2" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1624,7 +1580,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1655,51 +1611,51 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.238641062532729</v>
+        <v>10.42094195032128</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.8003448020753167</v>
+        <v>-0.2959236971464569</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.2902464771828116</v>
+        <v>-0.3816212997058296</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.0941874374009169</v>
+        <v>0.09006916199086408</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1074695015079701</v>
+        <v>0.16700821819378</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.8729054245952854</v>
+        <v>0.9051405850610622</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.04294998108173242</v>
+        <v>0.09106385411656848</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.1961608904197224</v>
+        <v>0.3962603760043311</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.2673921090207879</v>
+        <v>0.5571615261360007</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>0.1479776137116744</v>
+        <v>0.2386236150517921</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>1.799010124146353</v>
+        <v>1.202487454156597</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="X9" s="2" t="n">
@@ -1711,15 +1667,15 @@
         </is>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AB9" s="2" t="n">
-        <v>-0.7482615961872359</v>
+        <v>-0.1122542939773333</v>
       </c>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="n">
@@ -1731,11 +1687,11 @@
         </is>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AH9" s="2" t="n">
@@ -1752,167 +1708,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>10.42094195032128</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.2959236971464569</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.3816212997058296</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.09006916199086408</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.16700821819378</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9051405850610622</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>0.09106385411656848</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.3962603760043311</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.5571615261360007</v>
-      </c>
-      <c r="T10" s="3" t="n">
-        <v>0.2386236150517921</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>1.202487454156597</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>-0.1122542939773333</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>0.02170230059595868</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AF10" s="2" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="AH10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AJ10" s="2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AL10" s="2" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AN10" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1925,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2305,12 +2100,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2320,7 +2115,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2331,68 +2126,72 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.4836144302039722</v>
+        <v>0.3139603257403589</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.6365165293445558</v>
+        <v>0.4493777818549671</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.3100613758801871</v>
+        <v>-0.0841016075929526</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.08703159251923893</v>
+        <v>0.02699761172158303</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1493056045470308</v>
+        <v>0.08263477682588259</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9412742382271468</v>
+        <v>0.9484764542936288</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.154578844788938</v>
+        <v>0.04020490938000032</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.5965164192632566</v>
+        <v>0.9643513850902141</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.3285703899194556</v>
+        <v>-0.08545893048754642</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.3100613758801871</v>
+        <v>-0.0841016075929526</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.7548820739334152</v>
+        <v>0.263174509071993</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.02505461866766034</v>
+        <v>-0.2621596152012265</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.060244241089977</v>
+        <v>0.3696329099343196</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1156623821440808</v>
+        <v>-0.07500969632701393</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.1211878252333543</v>
+        <v>-0.00702211432575317</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.1319285426936267</v>
+        <v>0.392723165158209</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.009488865290659843</v>
+        <v>-0.2870242195178485</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -2408,7 +2207,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2439,62 +2238,62 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.3139603257403589</v>
+        <v>0.3342637880069268</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.4493777818549671</v>
+        <v>0.4717737298355982</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.0841016075929526</v>
+        <v>-0.3151750809469517</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.02699761172158303</v>
+        <v>0.0912445294782781</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.08263477682588259</v>
+        <v>0.1492559795343648</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9484764542936288</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.04020490938000032</v>
+        <v>-0.2253011823700724</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.9643513850902141</v>
+        <v>0.4629624237652712</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.08545893048754642</v>
+        <v>0.4788966914698187</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.0841016075929526</v>
+        <v>-0.3151750809469517</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.263174509071993</v>
+        <v>0.7223000185916155</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2621596152012265</v>
+        <v>0.006022920293228928</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.3696329099343196</v>
+        <v>1.01448221052669</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.07500969632701393</v>
+        <v>-0.1156623821440808</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.00702211432575317</v>
+        <v>0.008321491290317118</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.392723165158209</v>
+        <v>0.03723889361083943</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.2870242195178485</v>
+        <v>-0.02787921133564031</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -2510,7 +2309,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2528,89 +2327,79 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.3342637880069268</v>
+        <v>0.06680396301903335</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.4717737298355982</v>
+        <v>0.1767493517914234</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3151750809469517</v>
+        <v>-0.4201681847926452</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.0912445294782781</v>
+        <v>0.2134335215684736</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1492559795343648</v>
+        <v>0.1414862183727991</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9922437673130194</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.2253011823700724</v>
+        <v>-0.3197421967649414</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.4629624237652712</v>
+        <v>0.2846174306172771</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.4788966914698187</v>
+        <v>0.6796390438045132</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.3151750809469517</v>
+        <v>-0.4201681847926452</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.7223000185916155</v>
+        <v>0.5682348044310583</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.006022920293228928</v>
+        <v>-0.08396902942070572</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>1.01448221052669</v>
+        <v>0.7980950929801254</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1156623821440808</v>
+        <v>-0.1129397569157259</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.008321491290317118</v>
+        <v>-0.1938015761391647</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.03723889361083943</v>
+        <v>-0.08920752795735987</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.02787921133564031</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>-0.1006667494980568</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>-0.08365338050179061</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>-0.01856652126417235</v>
-      </c>
+        <v>-0.1148385075551088</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
     </row>
@@ -2622,7 +2411,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2653,62 +2442,62 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.06680396301903335</v>
+        <v>0.3287162064478732</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.1767493517914234</v>
+        <v>0.4656544115447738</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.4201681847926452</v>
+        <v>-0.3463388996218203</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.2134335215684736</v>
+        <v>0.1058820202873022</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1414862183727991</v>
+        <v>0.1523186628146193</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9922437673130194</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.3197421967649414</v>
+        <v>-0.2555931134354642</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.2846174306172771</v>
+        <v>0.4057583131051645</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.6796390438045132</v>
+        <v>0.5432847493257236</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.4201681847926452</v>
+        <v>-0.3463388996218203</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.5682348044310583</v>
+        <v>0.7849327168102194</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.08396902942070572</v>
+        <v>0.04260767863240034</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.7980950929801254</v>
+        <v>1.102450861370635</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1129397569157259</v>
+        <v>-0.1164761078434789</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.1938015761391647</v>
+        <v>0.004129107624539108</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>-0.08920752795735987</v>
+        <v>-0.003318763569698735</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1148385075551088</v>
+        <v>0.007472671223262006</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -2724,7 +2513,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2742,89 +2531,79 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.3287162064478732</v>
+        <v>0.2583720207707614</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.4656544115447738</v>
+        <v>0.3880605163519042</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.3463388996218203</v>
+        <v>-0.2055959130438868</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1058820202873022</v>
+        <v>0.1012281032702917</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1523186628146193</v>
+        <v>0.09903070490440699</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9268698060941828</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.2555931134354642</v>
+        <v>-0.1273043246721276</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.4057583131051645</v>
+        <v>0.6480223686065079</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.5432847493257236</v>
+        <v>0.2705960938773121</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.3463388996218203</v>
+        <v>-0.1922051192979058</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.7849327168102194</v>
+        <v>0.4419368129651728</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.04260767863240034</v>
+        <v>-0.1577417013304347</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.102450861370635</v>
+        <v>0.6207074946560626</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1164761078434789</v>
+        <v>-0.07500969632701404</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.004129107624539108</v>
+        <v>-0.04903096075406865</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>-0.003318763569698735</v>
+        <v>0.1684462092059837</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>0.007472671223262006</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>-0.1044059835241715</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>-0.1194839613651585</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0.01712402407157088</v>
-      </c>
+        <v>-0.18612510207709</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
     </row>
@@ -2836,7 +2615,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2867,180 +2646,68 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.2583720207707614</v>
+        <v>0.3547571291477991</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.3880605163519042</v>
+        <v>0.4943791257091903</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.2055959130438868</v>
+        <v>-0.3401599263032039</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1012281032702917</v>
+        <v>0.1055033703753101</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.09903070490440699</v>
+        <v>0.1505445811565411</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9268698060941828</v>
+        <v>0.9462603878116344</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.1273043246721276</v>
+        <v>-0.2324202616361078</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.6480223686065079</v>
+        <v>0.4495185598777809</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.2705960938773121</v>
+        <v>0.4940288957083911</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1922051192979058</v>
+        <v>-0.3401599263032039</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.4419368129651728</v>
+        <v>0.7649724991900968</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1577417013304347</v>
+        <v>0.03094859705362607</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.6207074946560626</v>
+        <v>1.074416408688024</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.07500969632701404</v>
+        <v>-0.1156623821440808</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.04903096075406865</v>
+        <v>0.02380859098261467</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.1684462092059837</v>
+        <v>0.02770720757571499</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.18612510207709</v>
+        <v>-0.003793509050400767</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.3547571291477991</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>0.4943791257091903</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.3401599263032039</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.1055033703753101</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.1505445811565411</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9462603878116344</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.2324202616361078</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.4495185598777809</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.4940288957083911</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.3401599263032039</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.7649724991900968</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>0.03094859705362607</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>1.074416408688024</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.1156623821440808</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>0.02380859098261467</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.02770720757571499</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.003793509050400767</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>-0.08685363153178371</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>-0.09207412940564097</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.005749916422626011</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3053,7 +2720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3433,12 +3100,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3448,7 +3115,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3459,74 +3126,82 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.4350331494949515</v>
+        <v>0.1006115993414891</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.3622676312689921</v>
+        <v>0.04480342973943419</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.1506103472912015</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1166796953447241</v>
+        <v>0.04829288677382208</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1997642353548091</v>
+        <v>0.07724581697211373</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9244186046511628</v>
+        <v>0.3466569767441861</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.3674998761946072</v>
+        <v>0.02220992715952153</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.2739414126958895</v>
+        <v>1.058870045499049</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7298771057515232</v>
+        <v>-0.04411026616389809</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.3674998761946072</v>
+        <v>0</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1.268826669726443</v>
+        <v>0.07669821051320369</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.06933303030489379</v>
+        <v>-0.4925355138254077</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>1.13114252804588</v>
+        <v>0.06837546042061436</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1170212548420333</v>
+        <v>-0.1506103472912013</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.120865585606033</v>
+        <v>-0.1403420434887794</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.1375572366932849</v>
+        <v>0.8384538694854164</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.01467324065008968</v>
+        <v>-0.532401671437185</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="n">
+        <v>0.1241816912769598</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>-0.08939590726649083</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3536,7 +3211,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3567,62 +3242,62 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.1006115993414891</v>
+        <v>0.3767591451106707</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.04480342973943419</v>
+        <v>0.306948498087245</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1506103472912015</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.04829288677382208</v>
+        <v>0.1170715483255394</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.07724581697211373</v>
+        <v>0.2012418815986788</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.3466569767441861</v>
+        <v>0.9280523255813954</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.02220992715952153</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>1.058870045499049</v>
+        <v>0.2739414126958895</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.04411026616389809</v>
+        <v>0.7298771057515232</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.07669821051320369</v>
+        <v>1.176693874504713</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.4925355138254077</v>
+        <v>0.02590942178534528</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.06837546042061436</v>
+        <v>1.049007335438753</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.1506103472912013</v>
+        <v>-0.1240889646699911</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.1403420434887794</v>
+        <v>0.07534933667980903</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.8384538694854164</v>
+        <v>0.1375572366932849</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.532401671437185</v>
+        <v>-0.05468551208403816</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -3631,7 +3306,7 @@
         <v>0.1241816912769598</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.08939590726649083</v>
+        <v>0.01312838014984941</v>
       </c>
     </row>
     <row r="6">
@@ -3642,7 +3317,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3660,95 +3335,81 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.3767591451106707</v>
+        <v>0.2548427792228856</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.306948498087245</v>
+        <v>0.1912140852415709</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.2697487878045376</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1170715483255394</v>
+        <v>0.07755375275567253</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2012418815986788</v>
+        <v>0.1316538674840658</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9280523255813954</v>
+        <v>0.9447674418604651</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.2697487878045377</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.2739414126958895</v>
+        <v>0.4708254210135241</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.7298771057515232</v>
+        <v>0.5357374989114265</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.2697487878045376</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>1.176693874504713</v>
+        <v>0.7183713744894256</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.02590942178534528</v>
+        <v>-0.1901050469873418</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>1.049007335438753</v>
+        <v>0.6404187679873986</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1240889646699911</v>
+        <v>-0.1506103472912023</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.07534933667980903</v>
+        <v>-0.01987623974249531</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.1375572366932849</v>
+        <v>0.3133634599770951</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.05468551208403816</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>-0.04060812421287263</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>-0.04060812421287274</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>0.1241816912769598</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>0.01312838014984941</v>
-      </c>
+        <v>-0.2537299916394827</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3758,7 +3419,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3789,62 +3450,62 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.2548427792228856</v>
+        <v>0.3346239523638623</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.1912140852415709</v>
+        <v>0.2669498337801117</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.2697487878045376</v>
+        <v>-0.4000942896051511</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.07755375275567253</v>
+        <v>0.1337899294054988</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1316538674840658</v>
+        <v>0.2052979460801001</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9447674418604651</v>
+        <v>0.9382267441860465</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.2697487878045377</v>
+        <v>-0.4000942896051513</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.4708254210135241</v>
+        <v>0.2082918238603966</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.5357374989114265</v>
+        <v>0.7946115932025033</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.2697487878045376</v>
+        <v>-0.4000942896051511</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.7183713744894256</v>
+        <v>1.224722867674378</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1901050469873418</v>
+        <v>0.04854622762596184</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.6404187679873986</v>
+        <v>1.091824560241528</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1506103472912023</v>
+        <v>-0.1240889646699911</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.01987623974249531</v>
+        <v>0.04243867708327231</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.3133634599770951</v>
+        <v>0.07893588713866384</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.2537299916394827</v>
+        <v>-0.03382704245029977</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -3860,7 +3521,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3878,89 +3539,79 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.3346239523638623</v>
+        <v>0.1520450866852068</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.2669498337801117</v>
+        <v>0.09362890460479822</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.4000942896051511</v>
+        <v>-0.1268809698977617</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1337899294054988</v>
+        <v>0.05975876723144954</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2052979460801001</v>
+        <v>0.1055520961703095</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9382267441860465</v>
+        <v>0.9680232558139535</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.4000942896051513</v>
+        <v>-0.04772465519664792</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.2082918238603966</v>
+        <v>0.91801226968219</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.7946115932025033</v>
+        <v>0.09478406787128581</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.4000942896051511</v>
+        <v>-0.08264378139658068</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>1.224722867674378</v>
+        <v>0.2097814912168157</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.04854622762596184</v>
+        <v>-0.4298113094000123</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1.091824560241528</v>
+        <v>0.187017479986753</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1240889646699911</v>
+        <v>-0.1268809698977618</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.04243867708327231</v>
+        <v>-0.10016873743549</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.07893588713866384</v>
+        <v>0.7126758857978428</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.03382704245029977</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>-0.06996994959066094</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>-0.05153265933679507</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>-0.01943903544530468</v>
-      </c>
+        <v>-0.4746050493112844</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
     </row>
@@ -3972,7 +3623,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4003,180 +3654,68 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.1520450866852068</v>
+        <v>0.3739350848273759</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.09362890460479822</v>
+        <v>0.3042676360360523</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1268809698977617</v>
+        <v>-0.3816212997058295</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.05975876723144954</v>
+        <v>0.1282330145072259</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1055520961703095</v>
+        <v>0.2029190381317474</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9680232558139535</v>
+        <v>0.9324127906976745</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.04772465519664792</v>
+        <v>-0.3816212997058296</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.91801226968219</v>
+        <v>0.2454989420305418</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.09478406787128581</v>
+        <v>0.7579231117208002</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.08264378139658068</v>
+        <v>-0.3816212997058295</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.2097814912168157</v>
+        <v>1.221834426337418</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.4298113094000123</v>
+        <v>0.04718486063882166</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.187017479986753</v>
+        <v>1.089249552232983</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.1268809698977618</v>
+        <v>-0.1240889646699911</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.10016873743549</v>
+        <v>0.0731435395633202</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.7126758857978428</v>
+        <v>0.1121597278185764</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.4746050493112844</v>
+        <v>-0.03508146112409927</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.3739350848273759</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>0.3042676360360523</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.3816212997058295</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.1282330145072259</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.2029190381317474</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9324127906976745</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.3816212997058296</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.2454989420305418</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.7579231117208002</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.3816212997058295</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>1.221834426337418</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>0.04718486063882166</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>1.089249552232983</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.1240889646699911</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>0.0731435395633202</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.1121597278185764</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.03508146112409927</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>-0.04257606501221145</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>-0.02232635691240947</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>-0.02071213460951193</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4189,7 +3728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4569,12 +4108,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4584,7 +4123,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4595,74 +4134,82 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.004463254504794456</v>
+        <v>0.0298093061781104</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.01851322395813138</v>
+        <v>0.006253052389626035</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1424709615053656</v>
+        <v>-0.1410541034597298</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.04623052871931452</v>
+        <v>0.04245763481668412</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1529248250153883</v>
+        <v>0.1639310826911156</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9862068965517241</v>
+        <v>0.8758620689655172</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1350492147242663</v>
+        <v>-0.133289881480832</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.07505645280409468</v>
+        <v>0.07724314664631593</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.691011962901241</v>
+        <v>0.6820099089431698</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1424709615053656</v>
+        <v>-0.1410541034597298</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1612952685910172</v>
+        <v>0.1881819355445027</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.08703698909779678</v>
+        <v>-0.06589978732071489</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.5929822223968276</v>
+        <v>0.6918277475147857</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.02174145290462626</v>
+        <v>-0.02330447460112961</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.01934565735807103</v>
+        <v>0.00539961384104104</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.003358755051266149</v>
+        <v>0.00539961384104104</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.02262840912588382</v>
+        <v>0</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="n">
+        <v>0.1656098075061709</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>-0.1340945703114591</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4672,7 +4219,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4703,41 +4250,41 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.0298093061781104</v>
+        <v>0.02279446582962819</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.006253052389626035</v>
+        <v>-0.0006013278051721915</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1410541034597298</v>
+        <v>-0.1410541034597297</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.04245763481668412</v>
+        <v>0.04297635660365116</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1639310826911156</v>
+        <v>0.164545871413997</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.8758620689655172</v>
+        <v>0.9241379310344827</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.133289881480832</v>
+        <v>-0.1391937251083381</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.07724314664631593</v>
+        <v>0.06990519713965893</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.6820099089431698</v>
+        <v>0.7122183524504826</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.1410541034597298</v>
+        <v>-0.1410541034597297</v>
       </c>
       <c r="U5" s="2" t="n">
         <v>0.1881819355445027</v>
@@ -4752,10 +4299,10 @@
         <v>-0.02330447460112961</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.00539961384104104</v>
+        <v>-0.001448952913220447</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.00539961384104104</v>
+        <v>-0.001448952913220558</v>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0</v>
@@ -4767,7 +4314,7 @@
         <v>0.1656098075061709</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.1340945703114591</v>
+        <v>0.009509211625454705</v>
       </c>
     </row>
     <row r="6">
@@ -4778,7 +4325,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4796,95 +4343,81 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.02279446582962819</v>
+        <v>-0.05929390134432888</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.0006013278051721915</v>
+        <v>-0.08081197412476204</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>-0.1410541034597297</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.04297635660365116</v>
+        <v>0.06505625151393715</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.164545871413997</v>
+        <v>0.1446920916972296</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9241379310344827</v>
+        <v>0.9793103448275862</v>
       </c>
       <c r="P6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.1391937251083381</v>
+        <v>-0.1379446474939671</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.06990519713965893</v>
+        <v>0.07145768887935322</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.7122183524504826</v>
+        <v>0.7058271448015913</v>
       </c>
       <c r="T6" s="2" t="n">
         <v>-0.1410541034597297</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.1881819355445027</v>
+        <v>0.09123630625457757</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.06589978732071489</v>
+        <v>-0.142114489992951</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.6918277475147857</v>
+        <v>0.3354190616917451</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.005137027073558564</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.001448952913220447</v>
+        <v>-0.08159156976704773</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>-0.001448952913220558</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>0.01824975801018347</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>-0.004791614106403164</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>0.02315230904721299</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>0.1656098075061709</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>0.009509211625454705</v>
-      </c>
+        <v>-0.08159156976704773</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4894,7 +4427,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4925,29 +4458,29 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.05929390134432888</v>
+        <v>0.01405857042339642</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.08081197412476204</v>
+        <v>-0.009137394982988933</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>-0.1410541034597297</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.06505625151393715</v>
+        <v>0.04425890301470417</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1446920916972296</v>
+        <v>0.1618643459723566</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9793103448275862</v>
+        <v>0.9586206896551724</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
         <v>-0.1379446474939671</v>
@@ -4962,25 +4495,25 @@
         <v>-0.1410541034597297</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.09123630625457757</v>
+        <v>0.176326517172573</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.142114489992951</v>
+        <v>-0.07522003407025546</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.3354190616917451</v>
+        <v>0.6482427595914475</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.005137027073558564</v>
+        <v>-0.02015312857781404</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.08159156976704773</v>
+        <v>-0.009977780352717347</v>
       </c>
       <c r="Z7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.08159156976704773</v>
+        <v>-0.009977780352717458</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -4996,7 +4529,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5014,89 +4547,79 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.01405857042339642</v>
+        <v>-0.0592939013443291</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.009137394982988933</v>
+        <v>-0.08081197412476226</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.04425890301470417</v>
+        <v>0.06505625151393719</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1618643459723566</v>
+        <v>0.1446920916972295</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9586206896551724</v>
+        <v>0.9793103448275862</v>
       </c>
       <c r="P8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.1379446474939672</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.07145768887935322</v>
+        <v>0.071457688879353</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.7058271448015913</v>
+        <v>0.7058271448015918</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.176326517172573</v>
+        <v>0.09123630625457735</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.07522003407025546</v>
+        <v>-0.1421144899929511</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.6482427595914475</v>
+        <v>0.3354190616917443</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.02015312857781404</v>
+        <v>-0.005137027073558564</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.009977780352717347</v>
+        <v>-0.08159156976704796</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.009977780352717458</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>0.009552679877107506</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>-0.003347511579838258</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0.01294352004016419</v>
-      </c>
+        <v>-0.08159156976704796</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
     </row>
@@ -5108,7 +4631,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5139,180 +4662,68 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.0592939013443291</v>
+        <v>0.01405857042339642</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.08081197412476226</v>
+        <v>-0.009137394982988933</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1410541034597296</v>
+        <v>-0.1410541034597297</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.06505625151393719</v>
+        <v>0.04425890301470417</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1446920916972295</v>
+        <v>0.1618643459723566</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9793103448275862</v>
+        <v>0.9586206896551724</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.1379446474939672</v>
+        <v>-0.1379446474939671</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.071457688879353</v>
+        <v>0.07145768887935322</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.7058271448015918</v>
+        <v>0.7058271448015913</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1410541034597296</v>
+        <v>-0.1410541034597297</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.09123630625457735</v>
+        <v>0.176326517172573</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1421144899929511</v>
+        <v>-0.07522003407025546</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.3354190616917443</v>
+        <v>0.6482427595914475</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.005137027073558564</v>
+        <v>-0.02015312857781404</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.08159156976704796</v>
+        <v>-0.009977780352717347</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.08159156976704796</v>
+        <v>-0.009977780352717458</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.01405857042339642</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.009137394982988933</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.1410541034597297</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.04425890301470417</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.1618643459723566</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9586206896551724</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.1379446474939671</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.07145768887935322</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.7058271448015913</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.1410541034597297</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.176326517172573</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>-0.07522003407025546</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>0.6482427595914475</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.02015312857781404</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>-0.009977780352717347</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.009977780352717458</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>0.009552679877107506</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>-0.003347511579838258</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.01294352004016419</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5325,7 +4736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5705,12 +5116,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5720,7 +5131,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5731,68 +5142,72 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.005869330943017559</v>
+        <v>-0.2241399968958406</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.08376291105473144</v>
+        <v>-0.2932762846971693</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2845422957875736</v>
+        <v>-0.290246477182812</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1140968231800305</v>
+        <v>0.2118873802483123</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.4114240812492495</v>
+        <v>0.3766351040867174</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>1</v>
       </c>
       <c r="P4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2845422957875736</v>
+        <v>-0.290246477182812</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.007998698566999085</v>
+        <v>-3.784557661279386e-05</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.980437851023039</v>
+        <v>1.000092557658176</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2845422957875736</v>
+        <v>-0.290246477182812</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.4059102655834499</v>
+        <v>0.09314005237279877</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.09103346041238103</v>
+        <v>-0.2932495373183879</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.7424559969061268</v>
+        <v>0.170363738736532</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.08544765322886072</v>
+        <v>-0.05160411514521168</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.001159757621766455</v>
+        <v>-0.2295617634294518</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.008036848302769961</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.00912328347919078</v>
+        <v>-0.2295617634294517</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -5808,7 +5223,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5839,23 +5254,23 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.2241399968958406</v>
+        <v>-0.01033194945437088</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.2932762846971693</v>
+        <v>-0.09852050782385913</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.290246477182812</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.2118873802483123</v>
+        <v>0.1248781540722552</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.3766351040867174</v>
+        <v>0.4262985277848752</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>1</v>
@@ -5864,37 +5279,37 @@
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.290246477182812</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-3.784557661279386e-05</v>
+        <v>-3.784557661268284e-05</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>1.000092557658176</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.290246477182812</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.09314005237279877</v>
+        <v>0.3943827240439621</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2932495373183879</v>
+        <v>-0.09848638952144639</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.170363738736532</v>
+        <v>0.721370813624854</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.05160411514521168</v>
+        <v>-0.08544765322886083</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.2295617634294518</v>
+        <v>-0.01724782228499044</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.2295617634294517</v>
+        <v>-0.01724782228499044</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -5910,7 +5325,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5928,40 +5343,36 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.01033194945437088</v>
+        <v>-0.2241399968958404</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.09852050782385913</v>
+        <v>-0.293276284697169</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>-0.2902464771828119</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.1248781540722552</v>
+        <v>0.2118873802483122</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.4262985277848752</v>
+        <v>0.3766351040867174</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>1</v>
@@ -5982,35 +5393,29 @@
         <v>-0.2902464771828119</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.3943827240439621</v>
+        <v>0.09314005237279877</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.09848638952144639</v>
+        <v>-0.2932495373183879</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.721370813624854</v>
+        <v>0.170363738736532</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.08544765322886083</v>
+        <v>-0.05160411514521168</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.01724782228499044</v>
+        <v>-0.2295617634294516</v>
       </c>
       <c r="Z6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.01724782228499044</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>-0.01610674458301609</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>-0.007972772340913536</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>-0.008199343743111376</v>
-      </c>
+        <v>-0.2295617634294517</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
       <c r="AE6" s="2" t="inlineStr"/>
       <c r="AF6" s="2" t="inlineStr"/>
     </row>
@@ -6022,7 +5427,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6053,23 +5458,23 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.2241399968958404</v>
+        <v>-0.01033194945437088</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.293276284697169</v>
+        <v>-0.09852050782385913</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>-0.2902464771828119</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.2118873802483122</v>
+        <v>0.1248781540722552</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.3766351040867174</v>
+        <v>0.4262985277848752</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>1</v>
@@ -6090,25 +5495,25 @@
         <v>-0.2902464771828119</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.09314005237279877</v>
+        <v>0.3943827240439621</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.2932495373183879</v>
+        <v>-0.09848638952144639</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.170363738736532</v>
+        <v>0.721370813624854</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.05160411514521168</v>
+        <v>-0.08544765322886083</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.2295617634294516</v>
+        <v>-0.01724782228499044</v>
       </c>
       <c r="Z7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.2295617634294517</v>
+        <v>-0.01724782228499044</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -6124,7 +5529,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6142,40 +5547,36 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.01033194945437088</v>
+        <v>-0.2241399968958403</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.09852050782385913</v>
+        <v>-0.2932762846971689</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.2902464771828118</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1248781540722552</v>
+        <v>0.2118873802483121</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.4262985277848752</v>
+        <v>0.3766351040867174</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>1</v>
@@ -6184,47 +5585,41 @@
         <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.2902464771828118</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-3.784557661268284e-05</v>
+        <v>-3.78455766124608e-05</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.000092557658176</v>
+        <v>1.000092557658175</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.2902464771828118</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.3943827240439621</v>
+        <v>0.09314005237279899</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.09848638952144639</v>
+        <v>-0.2932495373183877</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.721370813624854</v>
+        <v>0.1703637387365324</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.08544765322886083</v>
+        <v>-0.05160411514521168</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.01724782228499044</v>
+        <v>-0.2295617634294514</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.01724782228499044</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>-0.01610674458301609</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>-0.007972772340913536</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>-0.008199343743111376</v>
-      </c>
+        <v>-0.2295617634294516</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="inlineStr"/>
       <c r="AF8" s="2" t="inlineStr"/>
     </row>
@@ -6236,7 +5631,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6267,23 +5662,23 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.2241399968958403</v>
+        <v>-0.01033194945437088</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.2932762846971689</v>
+        <v>-0.09852050782385913</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.2902464771828118</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.2118873802483121</v>
+        <v>0.1248781540722552</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.3766351040867174</v>
+        <v>0.4262985277848752</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>1</v>
@@ -6292,155 +5687,43 @@
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.2902464771828118</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>-3.78455766124608e-05</v>
+        <v>-3.784557661268284e-05</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1.000092557658175</v>
+        <v>1.000092557658176</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.2902464771828118</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.09314005237279899</v>
+        <v>0.3943827240439621</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.2932495373183877</v>
+        <v>-0.09848638952144639</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.1703637387365324</v>
+        <v>0.721370813624854</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.05160411514521168</v>
+        <v>-0.08544765322886083</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.2295617634294514</v>
+        <v>-0.01724782228499044</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.2295617634294516</v>
+        <v>-0.01724782228499044</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="inlineStr"/>
       <c r="AF9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>-0.01033194945437088</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.09852050782385913</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.1248781540722552</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.4262985277848752</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>-3.784557661268284e-05</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>1.000092557658176</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.3943827240439621</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>-0.09848638952144639</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>0.721370813624854</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.08544765322886083</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>-0.01724782228499044</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.01724782228499044</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>-0.01610674458301609</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>-0.007972772340913536</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>-0.008199343743111376</v>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6453,7 +5736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6833,12 +6116,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6848,7 +6131,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -6859,74 +6142,82 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0.008347989224310126</v>
+        <v>-0.03396006753160985</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.06537597639031245</v>
+        <v>-0.0895151536626404</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2217386103320992</v>
+        <v>-0.2093348703683601</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1202141404246801</v>
+        <v>0.1087073838403099</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1643665908468291</v>
+        <v>0.1474926725482544</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1</v>
+        <v>0.8791423001949318</v>
       </c>
       <c r="P4" t="b">
         <v>0</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2214796402899178</v>
+        <v>-0.2055463545127731</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.128014615636332</v>
+        <v>0.1511006904031149</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.7148394203240476</v>
+        <v>0.6634137418558945</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2217386103320992</v>
+        <v>-0.2093348703683601</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.2737650318419123</v>
+        <v>0.2159802374321436</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.1714433388946379</v>
+        <v>-0.2090311004691446</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.5094914103593154</v>
+        <v>0.4019508081024246</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.09083171626673225</v>
+        <v>-0.07741687217408399</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.06561287296405904</v>
+        <v>-0.08974593174569512</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.02122573303220254</v>
+        <v>0.04212625444366003</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.08503370331104199</v>
+        <v>-0.1265414681062376</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="n">
+        <v>0.678953431147129</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>-0.4035884689523094</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6936,7 +6227,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6967,62 +6258,62 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.03396006753160985</v>
+        <v>-0.001898460228708654</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.0895151536626404</v>
+        <v>-0.05929734732007919</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.2093348703683601</v>
+        <v>-0.2378794616385039</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1087073838403099</v>
+        <v>0.125484862997163</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1474926725482544</v>
+        <v>0.1697461539198723</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.8791423001949318</v>
+        <v>1</v>
       </c>
       <c r="P5" t="b">
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.2055463545127731</v>
+        <v>-0.237879461638504</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.1511006904031149</v>
+        <v>0.1042525676124126</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.6634137418558945</v>
+        <v>0.7677708715892542</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.2093348703683601</v>
+        <v>-0.2378794616385039</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.2159802374321436</v>
+        <v>0.3096373730028814</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2090311004691446</v>
+        <v>-0.1481091552144772</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.4019508081024246</v>
+        <v>0.576251761628526</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.07741687217408399</v>
+        <v>-0.09585156482023383</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.08974593174569512</v>
+        <v>-0.05953578462717246</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.04212625444366003</v>
+        <v>-0.0002867674045797797</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.1265414681062376</v>
+        <v>-0.05926601278325838</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -7031,7 +6322,7 @@
         <v>0.678953431147129</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.4035884689523094</v>
+        <v>-0.04772872481844626</v>
       </c>
     </row>
     <row r="6">
@@ -7042,7 +6333,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -7060,95 +6351,81 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.001898460228708654</v>
+        <v>0.1756491859378704</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.05929734732007919</v>
+        <v>0.1080398774719478</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.2378794616385039</v>
+        <v>-0.1215847395419751</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.125484862997163</v>
+        <v>0.03482783726599165</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1697461539198723</v>
+        <v>0.08867046039686673</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1</v>
+        <v>0.9103313840155945</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.237879461638504</v>
+        <v>-0.03144317402540209</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.1042525676124126</v>
+        <v>0.4033624710605406</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.7677708715892542</v>
+        <v>0.101484814875283</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.2378794616385039</v>
+        <v>-0.1215847395419751</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.3096373730028814</v>
+        <v>0.2138153946258015</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1481091552144772</v>
+        <v>-0.210439283990125</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.576251761628526</v>
+        <v>0.3979219195070163</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.09585156482023383</v>
+        <v>-0.07741687217408422</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.05953578462717246</v>
+        <v>0.1077590256599712</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>-0.0002867674045797797</v>
+        <v>0.2705064707075802</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.05926601278325838</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>0.006503822838574758</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>-0.02106537246462437</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>0.0281624477546667</v>
-      </c>
-      <c r="AE6" s="2" t="n">
-        <v>0.678953431147129</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>-0.04772872481844626</v>
-      </c>
+        <v>-0.1280965101712315</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7158,7 +6435,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7189,62 +6466,62 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.1756491859378704</v>
+        <v>0.02410497175343318</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.1080398774719478</v>
+        <v>-0.03478932236503507</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.1215847395419751</v>
+        <v>-0.222104966978485</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.03482783726599165</v>
+        <v>0.1188103428199329</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.08867046039686673</v>
+        <v>0.1666505507231491</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9103313840155945</v>
+        <v>0.9902534113060428</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.03144317402540209</v>
+        <v>-0.2218461188431556</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.4033624710605406</v>
+        <v>0.1274836171091729</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.101484814875283</v>
+        <v>0.7160222528237516</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.1215847395419751</v>
+        <v>-0.222104966978485</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.2138153946258015</v>
+        <v>0.3160699914918432</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.210439283990125</v>
+        <v>-0.1439248757248198</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.3979219195070163</v>
+        <v>0.5882232097137479</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.07741687217408422</v>
+        <v>-0.09083171626673225</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.1077590256599712</v>
+        <v>-0.03503397165362521</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.2705064707075802</v>
+        <v>0.02074500401271973</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1280965101712315</v>
+        <v>-0.05464535750561472</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -7260,7 +6537,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7278,91 +6555,85 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.02410497175343318</v>
+        <v>0.1313460375688129</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.03478932236503507</v>
+        <v>0.06628451738864993</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.222104966978485</v>
+        <v>-0.07741687217408422</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1188103428199329</v>
+        <v>0.01276474919454059</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1666505507231491</v>
+        <v>0.04922436856579283</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9902534113060428</v>
+        <v>0.2241715399610136</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.2218461188431556</v>
+        <v>0.01130377776197578</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.1274836171091729</v>
+        <v>0.465299433644307</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.7160222528237516</v>
+        <v>-0.036483651193696</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.222104966978485</v>
+        <v>0</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.3160699914918432</v>
+        <v>0.1187004957822777</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.1439248757248198</v>
+        <v>-0.2723094727903348</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.5882232097137479</v>
+        <v>0.2209079903286753</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.09083171626673225</v>
+        <v>-0.07741687217408433</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.03503397165362521</v>
+        <v>0.0660142491926401</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.02074500401271973</v>
+        <v>0.3265798753777083</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.05464535750561472</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>0.03272615859706463</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>-0.0004707372757396522</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0.03321253024881399</v>
-      </c>
-      <c r="AE8" s="2" t="inlineStr"/>
-      <c r="AF8" s="2" t="inlineStr"/>
+        <v>-0.196419100742712</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="n">
+        <v>0.09967003453281076</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>-0.09051009422763445</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7372,7 +6643,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7403,62 +6674,62 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.1313460375688129</v>
+        <v>0.006430108302580395</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.06628451738864993</v>
+        <v>-0.05144773863977858</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.07741687217408422</v>
+        <v>-0.2217386103320992</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.01276474919454059</v>
+        <v>0.120308212821147</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.04922436856579283</v>
+        <v>0.1643805444217967</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.2241715399610136</v>
+        <v>0.9980506822612085</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.01130377776197578</v>
+        <v>-0.2214796402899176</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.465299433644307</v>
+        <v>0.1280146156363324</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>-0.036483651193696</v>
+        <v>0.7148394203240468</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>0</v>
+        <v>-0.2217386103320992</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.1187004957822777</v>
+        <v>0.2927473196428292</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.2723094727903348</v>
+        <v>-0.1590957703813733</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.2209079903286753</v>
+        <v>0.5448184662600134</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.07741687217408433</v>
+        <v>-0.09083171626673225</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.0660142491926401</v>
+        <v>-0.05168816556553635</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.3265798753777083</v>
+        <v>0.02122573303220299</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.196419100742712</v>
+        <v>-0.07139841490406329</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -7467,122 +6738,6 @@
         <v>0.09967003453281076</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>-0.09051009422763445</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.006430108302580395</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.05144773863977858</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.2217386103320992</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.120308212821147</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.1643805444217967</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.9980506822612085</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.2214796402899176</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.1280146156363324</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.7148394203240468</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.2217386103320992</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.2927473196428292</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>-0.1590957703813733</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>0.5448184662600134</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.09083171626673225</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>-0.05168816556553635</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.02122573303220299</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.07139841490406329</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>0.01490250346523347</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>2.220446049250313e-16</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0.01490250346523325</v>
-      </c>
-      <c r="AE10" s="2" t="n">
-        <v>0.09967003453281076</v>
-      </c>
-      <c r="AF10" s="2" t="n">
         <v>-0.001640172913999871</v>
       </c>
     </row>
@@ -7597,7 +6752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7977,12 +7132,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -7992,7 +7147,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -8003,74 +7158,82 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0.0520480753590512</v>
+        <v>0.0148966629316607</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.04977130173806421</v>
+        <v>0.01733422320252109</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1245530606971786</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.0653683722520295</v>
+        <v>0</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2161775406597309</v>
+        <v>1.757200726823261e-05</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.1245530606971786</v>
+        <v>0.005700135266177409</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.1284458931702925</v>
+        <v>0.296341487361538</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.5555413873337464</v>
+        <v>-0.02542419299884729</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1245530606971786</v>
+        <v>0</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.08282053666881062</v>
+        <v>0.009144403329576001</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.1579315375127712</v>
+        <v>-0.2152266720452527</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.289677927852336</v>
+        <v>0.03198399714010956</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.04770979298828082</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.006478325044862898</v>
+        <v>0.06368456696172653</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.0349593358613034</v>
+        <v>0.1889455515140797</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.04003796040129592</v>
+        <v>-0.1053546854124969</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="n">
+        <v>0.10904401508735</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>-0.08356097205346547</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8080,7 +7243,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -8111,62 +7274,62 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>-0.05204807535905154</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.01733422320252109</v>
+        <v>-0.04977130173806454</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>-0.1245530606971789</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0</v>
+        <v>0.06536837225202972</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.216177540659731</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.1245530606971789</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.1284458931702923</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>0.5555413873337472</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0</v>
+        <v>-0.1245530606971789</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.08282053666881062</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.2152266720452527</v>
+        <v>-0.1579315375127712</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.03198399714010956</v>
+        <v>0.289677927852336</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0</v>
+        <v>-0.04770979298828082</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.06368456696172653</v>
+        <v>-0.006478325044863231</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.1889455515140797</v>
+        <v>0.03495933586130318</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.1053546854124969</v>
+        <v>-0.04003796040129592</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -8175,7 +7338,7 @@
         <v>0.10904401508735</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.08356097205346547</v>
+        <v>-0.03077953492302243</v>
       </c>
     </row>
     <row r="6">
@@ -8186,7 +7349,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -8204,94 +7367,84 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.05204807535905154</v>
+        <v>0.0148966629316607</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.04977130173806454</v>
+        <v>0.01733422320252109</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1245530606971789</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.06536837225202972</v>
+        <v>0</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.216177540659731</v>
+        <v>1.757200726823261e-05</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.1245530606971789</v>
+        <v>0.005700135266177409</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.1284458931702923</v>
+        <v>0.296341487361538</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.5555413873337472</v>
+        <v>-0.02542419299884729</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1245530606971789</v>
+        <v>0</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.08282053666881062</v>
+        <v>0.009144403329576001</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1579315375127712</v>
+        <v>-0.2152266720452527</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.289677927852336</v>
+        <v>0.03198399714010956</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.04770979298828082</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.006478325044863231</v>
+        <v>0.06368456696172653</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.03495933586130318</v>
+        <v>0.1889455515140797</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.04003796040129592</v>
-      </c>
-      <c r="AB6" s="2" t="n">
-        <v>-3.33066907387547e-16</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>-2.220446049250313e-16</v>
-      </c>
-      <c r="AD6" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.1053546854124969</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
       <c r="AE6" s="2" t="n">
-        <v>0.10904401508735</v>
+        <v>0.06587707306593193</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>-0.03077953492302243</v>
+        <v>-0.05707000491572445</v>
       </c>
     </row>
     <row r="7">
@@ -8302,7 +7455,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -8333,62 +7486,62 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>-0.05204807535905154</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.01733422320252109</v>
+        <v>-0.04977130173806454</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>-0.1245530606971789</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>0.06536837225202972</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.216177540659731</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.1245530606971789</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.1284458931702923</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>0.5555413873337472</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0</v>
+        <v>-0.1245530606971789</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.08282053666881062</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.2152266720452527</v>
+        <v>-0.1579315375127712</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.03198399714010956</v>
+        <v>0.289677927852336</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0</v>
+        <v>-0.04770979298828082</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.06368456696172653</v>
+        <v>-0.006478325044863231</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.1889455515140797</v>
+        <v>0.03495933586130318</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.1053546854124969</v>
+        <v>-0.04003796040129592</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -8397,7 +7550,7 @@
         <v>0.06587707306593193</v>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>-0.05707000491572445</v>
+        <v>0.002524249698548031</v>
       </c>
     </row>
     <row r="8">
@@ -8408,7 +7561,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -8426,94 +7579,84 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.05204807535905154</v>
+        <v>0.0148966629316607</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.04977130173806454</v>
+        <v>0.01733422320252109</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1245530606971789</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.06536837225202972</v>
+        <v>0</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.216177540659731</v>
+        <v>1.757200726823261e-05</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1245530606971789</v>
+        <v>0.005700135266177409</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.1284458931702923</v>
+        <v>0.296341487361538</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.5555413873337472</v>
+        <v>-0.02542419299884729</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1245530606971789</v>
+        <v>0</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.08282053666881062</v>
+        <v>0.009144403329576001</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.1579315375127712</v>
+        <v>-0.2152266720452527</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.289677927852336</v>
+        <v>0.03198399714010956</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.04770979298828082</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.006478325044863231</v>
+        <v>0.06368456696172653</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.03495933586130318</v>
+        <v>0.1889455515140797</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.04003796040129592</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>-3.33066907387547e-16</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>-2.220446049250313e-16</v>
-      </c>
-      <c r="AD8" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.1053546854124969</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="n">
-        <v>0.06587707306593193</v>
+        <v>0.10904401508735</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>0.002524249698548031</v>
+        <v>-0.08356097205346547</v>
       </c>
     </row>
     <row r="9">
@@ -8524,7 +7667,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -8555,62 +7698,62 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>-0.05204807535905154</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.01733422320252109</v>
+        <v>-0.04977130173806454</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>-0.1245530606971789</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>0.06536837225202972</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.216177540659731</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.1245530606971789</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.1284458931702923</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>0.5555413873337472</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>0</v>
+        <v>-0.1245530606971789</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.08282053666881062</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.2152266720452527</v>
+        <v>-0.1579315375127712</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.03198399714010956</v>
+        <v>0.289677927852336</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0</v>
+        <v>-0.04770979298828082</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.06368456696172653</v>
+        <v>-0.006478325044863231</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.1889455515140797</v>
+        <v>0.03495933586130318</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.1053546854124969</v>
+        <v>-0.04003796040129592</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -8619,122 +7762,6 @@
         <v>0.10904401508735</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>-0.08356097205346547</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>-0.05204807535905154</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>-0.04977130173806454</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-0.1245530606971789</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.06536837225202972</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>0.216177540659731</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>-0.1245530606971789</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>0.1284458931702923</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.5555413873337472</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>-0.1245530606971789</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0.08282053666881062</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>-0.1579315375127712</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>0.289677927852336</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>-0.04770979298828082</v>
-      </c>
-      <c r="Y10" s="2" t="n">
-        <v>-0.006478325044863231</v>
-      </c>
-      <c r="Z10" s="2" t="n">
-        <v>0.03495933586130318</v>
-      </c>
-      <c r="AA10" s="2" t="n">
-        <v>-0.04003796040129592</v>
-      </c>
-      <c r="AB10" s="2" t="n">
-        <v>-3.33066907387547e-16</v>
-      </c>
-      <c r="AC10" s="2" t="n">
-        <v>-2.220446049250313e-16</v>
-      </c>
-      <c r="AD10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="2" t="n">
-        <v>0.10904401508735</v>
-      </c>
-      <c r="AF10" s="2" t="n">
         <v>-0.03077953492302243</v>
       </c>
     </row>

--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_hrp_quarterly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_hrp_quarterly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -847,27 +848,27 @@
         <v>0.7822599407481463</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="n">
@@ -966,19 +967,19 @@
         <v>0.9520079944713302</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z4" s="2" t="n">
@@ -986,7 +987,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="n">
@@ -994,19 +995,19 @@
       </c>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH4" s="2" t="n">
@@ -1014,7 +1015,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="inlineStr"/>
@@ -1103,27 +1104,27 @@
         <v>0.89672861203617</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="n">
@@ -1131,19 +1132,19 @@
       </c>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH5" s="2" t="n">
@@ -1151,7 +1152,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="inlineStr"/>
@@ -1240,19 +1241,19 @@
         <v>1.554147077298945</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z6" s="2" t="n">
@@ -1260,7 +1261,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB6" s="2" t="n">
@@ -1268,19 +1269,19 @@
       </c>
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AH6" s="2" t="n">
@@ -1288,7 +1289,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ6" s="2" t="inlineStr"/>
@@ -1377,27 +1378,27 @@
         <v>1.058182916812717</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB7" s="2" t="n">
@@ -1405,27 +1406,27 @@
       </c>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AH7" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr"/>
@@ -1514,19 +1515,19 @@
         <v>1.799010124146353</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="X8" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z8" s="2" t="n">
@@ -1534,7 +1535,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="n">
@@ -1542,19 +1543,19 @@
       </c>
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH8" s="2" t="n">
@@ -1562,7 +1563,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ8" s="2" t="inlineStr"/>
@@ -1651,27 +1652,27 @@
         <v>1.202487454156597</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AB9" s="2" t="n">
@@ -1679,19 +1680,19 @@
       </c>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH9" s="2" t="n">
@@ -1699,7 +1700,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="inlineStr"/>
@@ -1950,28 +1951,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.09343144196766695</v>
+        <v>0.05644008609220919</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.4862309442441406</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2715577666208211</v>
+        <v>0.08831268540851211</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1809616537571158</v>
+        <v>0.2970580221997945</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9994459833795014</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.4704588408798214</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -1980,10 +1981,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.4862309442441406</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.7119888462278878</v>
+        <v>0.272403402144199</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -1992,7 +1993,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.139529174066894</v>
+        <v>-0.08310591627222996</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -2038,49 +2039,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.3232523550594082</v>
+        <v>0.07226254240722541</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.4596274527008404</v>
+        <v>0.01497714496384162</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.3309499985899496</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1029240628466189</v>
+        <v>0.080664311843716</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1531765783358609</v>
+        <v>0.2791637973599133</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9484764542936288</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.2531143766379184</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.4104392274304347</v>
+        <v>0.009378627607342649</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.538015984914983</v>
+        <v>0.9541220317503244</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.3309499985899496</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.7716934342675263</v>
+        <v>0.2794607860995721</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.03487440246540663</v>
+        <v>0.005546498809638756</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.083856072122412</v>
+        <v>1.0259078407238</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1209745732692815</v>
+        <v>-0.05531518128978974</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -2140,58 +2141,58 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.3139603257403589</v>
+        <v>-0.1251458276246117</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.4493777818549671</v>
+        <v>-0.1718847250377543</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.0841016075929526</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.02699761172158303</v>
+        <v>0.1068605087841051</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.08263477682588259</v>
+        <v>0.2473038288260035</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.9484764542936288</v>
+        <v>1</v>
       </c>
       <c r="P4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.04020490938000032</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.9643513850902141</v>
+        <v>0.009378627607342649</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.08545893048754642</v>
+        <v>0.9541220317503244</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.0841016075929526</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.263174509071993</v>
+        <v>0.04390628492625237</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.2621596152012265</v>
+        <v>-0.1795791467021333</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.3696329099343196</v>
+        <v>0.1611811180794659</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.07500969632701393</v>
+        <v>-0.04949284814011778</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.00702211432575317</v>
+        <v>-0.1841045100658427</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.392723165158209</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.2870242195178485</v>
+        <v>-0.1841045100658427</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
@@ -2242,58 +2243,58 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.3342637880069268</v>
+        <v>0.06185027983725977</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.4717737298355982</v>
+        <v>0.005121155299079083</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.3151750809469517</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.0912445294782781</v>
+        <v>0.07978614376250986</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1492559795343648</v>
+        <v>0.2767660712204212</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.2253011823700724</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.4629624237652712</v>
+        <v>0.009378627607342649</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.4788966914698187</v>
+        <v>0.9541220317503244</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.3151750809469517</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.7223000185916155</v>
+        <v>0.2670365139405022</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.006022920293228928</v>
+        <v>-0.004217914062987216</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>1.01448221052669</v>
+        <v>0.9802980133087479</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.1156623821440808</v>
+        <v>-0.04890306599166516</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.008321491290317118</v>
+        <v>-0.009710553300304792</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.03723889361083943</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.02787921133564031</v>
+        <v>-0.009710553300304903</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
@@ -2344,58 +2345,58 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.06680396301903335</v>
+        <v>-0.1251458276246117</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.1767493517914234</v>
+        <v>-0.1718847250377543</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.4201681847926452</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.2134335215684736</v>
+        <v>0.1068605087841051</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1414862183727991</v>
+        <v>0.2473038288260035</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9922437673130194</v>
+        <v>1</v>
       </c>
       <c r="P6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.3197421967649414</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.2846174306172771</v>
+        <v>0.009378627607342649</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.6796390438045132</v>
+        <v>0.9541220317503244</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.4201681847926452</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.5682348044310583</v>
+        <v>0.04390628492625237</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.08396902942070572</v>
+        <v>-0.1795791467021333</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.7980950929801254</v>
+        <v>0.1611811180794659</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1129397569157259</v>
+        <v>-0.04949284814011778</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.1938015761391647</v>
+        <v>-0.1841045100658427</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>-0.08920752795735987</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1148385075551088</v>
+        <v>-0.1841045100658427</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
@@ -2446,58 +2447,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.3287162064478732</v>
+        <v>0.06185027983725977</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.4656544115447738</v>
+        <v>0.005121155299079083</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.3463388996218203</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1058820202873022</v>
+        <v>0.07978614376250986</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1523186628146193</v>
+        <v>0.2767660712204212</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.2555931134354642</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.4057583131051645</v>
+        <v>0.009378627607342649</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.5432847493257236</v>
+        <v>0.9541220317503244</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.3463388996218203</v>
+        <v>-0.1619418476466084</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.7849327168102194</v>
+        <v>0.2670365139405022</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.04260767863240034</v>
+        <v>-0.004217914062987216</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>1.102450861370635</v>
+        <v>0.9802980133087479</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1164761078434789</v>
+        <v>-0.04890306599166516</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.004129107624539108</v>
+        <v>-0.009710553300304792</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>-0.003318763569698735</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>0.007472671223262006</v>
+        <v>-0.009710553300304903</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -2548,64 +2549,68 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.2583720207707614</v>
+        <v>0.01633146664688923</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.3880605163519042</v>
+        <v>-0.03796582501302315</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.2055959130438868</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.1012281032702917</v>
+        <v>0</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.09903070490440699</v>
+        <v>0.0002468489756377671</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9268698060941828</v>
+        <v>0</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1273043246721276</v>
+        <v>0.006089370624204005</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.6480223686065079</v>
+        <v>0.2117597153840087</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.2705960938773121</v>
+        <v>-0.03587709265072071</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1922051192979058</v>
+        <v>0</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.4419368129651728</v>
+        <v>0.01018010558677385</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.1577417013304347</v>
+        <v>-0.2060850325577076</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.6207074946560626</v>
+        <v>0.03737143334716841</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.07500969632701404</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.04903096075406865</v>
+        <v>-0.05216173609382191</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.1684462092059837</v>
+        <v>0.2005006666887683</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.18612510207709</v>
+        <v>-0.210464191977074</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr"/>
-      <c r="AE8" s="2" t="inlineStr"/>
-      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="n">
+        <v>0.0400589872135646</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>-0.0366163262770185</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2650,64 +2655,68 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.3547571291477991</v>
+        <v>0.06577286665514537</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.4943791257091903</v>
+        <v>0.008834178753532873</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.3401599263032039</v>
+        <v>-0.158845408661771</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1055033703753101</v>
+        <v>0.07957894723870017</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1505445811565411</v>
+        <v>0.2697343811059917</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9462603878116344</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.2324202616361078</v>
+        <v>-0.158845408661771</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.4495185598777809</v>
+        <v>0.01310805774796986</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.4940288957083911</v>
+        <v>0.9358785653558257</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.3401599263032039</v>
+        <v>-0.158845408661771</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.7649724991900968</v>
+        <v>0.2670356645852239</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.03094859705362607</v>
+        <v>-0.004218581583426806</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>1.074416408688024</v>
+        <v>0.9802948953033499</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.1156623821440808</v>
+        <v>-0.04142921346750827</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.02380859098261467</v>
+        <v>-0.006052319740192269</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.02770720757571499</v>
+        <v>0.003694778191873693</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.003793509050400767</v>
+        <v>-0.009711217138765327</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.0400589872135646</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>-0.008070410952093265</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2950,28 +2959,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.05341499464255506</v>
+        <v>-0.09123360655355239</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.5040024023286764</v>
+        <v>-0.4862309442441406</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.2216991067360366</v>
+        <v>0.2716992530341484</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2389480542019927</v>
+        <v>0.1810585772249194</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9832848837209303</v>
+        <v>1</v>
       </c>
       <c r="P2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.5035092528573126</v>
+        <v>-0.4707583434268603</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -2980,10 +2989,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.5040024023286764</v>
+        <v>-0.4862309442441406</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>1.12172130237064</v>
+        <v>0.7171104771509207</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -2992,7 +3001,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1530343433756415</v>
+        <v>-0.139529174066894</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -3038,49 +3047,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.2802901328432288</v>
+        <v>0.3294578948487177</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.21537109245123</v>
+        <v>0.4629259009092757</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3309499985899496</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1663071666219633</v>
+        <v>0.1029808820995737</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2118385751587301</v>
+        <v>0.1532558675077065</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9462209302325582</v>
+        <v>0.9484193011647255</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.4439839127181155</v>
+        <v>-0.2514292974161799</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.1198921439760285</v>
+        <v>0.414421357968767</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.8817790541059516</v>
+        <v>0.5340941927569753</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.4439839127181154</v>
+        <v>-0.3309499985899496</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1.302613471315189</v>
+        <v>0.7759950933958086</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.08525727141563522</v>
+        <v>0.03429285245675695</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>1.16126302367821</v>
+        <v>1.082113730200731</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.1240889646699911</v>
+        <v>-0.1209745732692815</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -3140,68 +3149,64 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.1006115993414891</v>
+        <v>0.3166781767849147</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.04480342973943419</v>
+        <v>0.4488631911128267</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1506103472912015</v>
+        <v>-0.0841016075929526</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.04829288677382208</v>
+        <v>0.02700708029875899</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.07724581697211373</v>
+        <v>0.08267572651261756</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.3466569767441861</v>
+        <v>0.9484193011647255</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.02220992715952153</v>
+        <v>0.04255175824724233</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>1.058870045499049</v>
+        <v>0.9698973905376336</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.04411026616389809</v>
+        <v>-0.09038981218577896</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0</v>
+        <v>-0.0841016075929526</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.07669821051320369</v>
+        <v>0.262937946599926</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.4925355138254077</v>
+        <v>-0.2644981418461617</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.06837546042061436</v>
+        <v>0.3666630944294361</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.1506103472912013</v>
+        <v>-0.07500969632701393</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.1403420434887794</v>
+        <v>-0.009612728701917428</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.8384538694854164</v>
+        <v>0.3927231651582093</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.532401671437185</v>
+        <v>-0.2888843267099837</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="n">
-        <v>0.1241816912769598</v>
-      </c>
-      <c r="AF4" s="2" t="n">
-        <v>-0.08939590726649083</v>
-      </c>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3246,68 +3251,64 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.3767591451106707</v>
+        <v>0.3390727829068065</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.306948498087245</v>
+        <v>0.4735060545410852</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.3151750809469518</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1170715483255394</v>
+        <v>0.0912948606856667</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.2012418815986788</v>
+        <v>0.1493349944699654</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9280523255813954</v>
+        <v>0.947310038824182</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.2235533526624697</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.2739414126958895</v>
+        <v>0.467092844439065</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.7298771057515232</v>
+        <v>0.4748792151725341</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.3151750809469518</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>1.176693874504713</v>
+        <v>0.7246166075911928</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.02590942178534528</v>
+        <v>0.004371373036361925</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>1.049007335438753</v>
+        <v>1.0104671883614</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.1240889646699911</v>
+        <v>-0.1156623821440808</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.07534933667980903</v>
+        <v>0.007232186965336673</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.1375572366932849</v>
+        <v>0.03723889361083943</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.05468551208403816</v>
+        <v>-0.02892940751676121</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="n">
-        <v>0.1241816912769598</v>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>0.01312838014984941</v>
-      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3352,58 +3353,58 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.2548427792228856</v>
+        <v>0.07180685941638032</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.1912140852415709</v>
+        <v>0.1794085555382505</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.2697487878045376</v>
+        <v>-0.4201681847926452</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.07755375275567253</v>
+        <v>0.2135516948409822</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1316538674840658</v>
+        <v>0.14155912646255</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9447674418604651</v>
+        <v>0.9922351636161952</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.2697487878045377</v>
+        <v>-0.3182074392949865</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.4708254210135241</v>
+        <v>0.2882443251342814</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.5357374989114265</v>
+        <v>0.6759464675200707</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.2697487878045376</v>
+        <v>-0.4201681847926452</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.7183713744894256</v>
+        <v>0.5720424674450382</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.1901050469873418</v>
+        <v>-0.08448379509429327</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.6404187679873986</v>
+        <v>0.7977047967807728</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.1506103472912023</v>
+        <v>-0.1129397569157259</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.01987623974249531</v>
+        <v>-0.1938015761391647</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.3133634599770951</v>
+        <v>-0.08920752795735976</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.2537299916394827</v>
+        <v>-0.1148385075551086</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
@@ -3454,58 +3455,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.3346239523638623</v>
+        <v>0.3349473695788412</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.2669498337801117</v>
+        <v>0.4689664794008559</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.4000942896051511</v>
+        <v>-0.3463388996218203</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1337899294054988</v>
+        <v>0.1059404848475645</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.2052979460801001</v>
+        <v>0.1523974335056746</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9382267441860465</v>
+        <v>0.947310038824182</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.4000942896051513</v>
+        <v>-0.2539136265932589</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.2082918238603966</v>
+        <v>0.4097272278937365</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.7946115932025033</v>
+        <v>0.5393714846239541</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.4000942896051511</v>
+        <v>-0.3463388996218203</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>1.224722867674378</v>
+        <v>0.789266520822882</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.04854622762596184</v>
+        <v>0.04202178289173597</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>1.091824560241528</v>
+        <v>1.100620540308708</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.1240889646699911</v>
+        <v>-0.1164761078434789</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.04243867708327231</v>
+        <v>0.004129107624539108</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.07893588713866384</v>
+        <v>-0.003318763569698735</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.03382704245029977</v>
+        <v>0.007472671223262006</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -3556,58 +3557,58 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.1520450866852068</v>
+        <v>0.2642732969822035</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.09362890460479822</v>
+        <v>0.3911972384756826</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1268809698977617</v>
+        <v>-0.2055959130438868</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.05975876723144954</v>
+        <v>0.1012839790174607</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1055520961703095</v>
+        <v>0.09907703823059845</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9680232558139535</v>
+        <v>0.9267886855241264</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.04772465519664792</v>
+        <v>-0.1253354002432755</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.91801226968219</v>
+        <v>0.6526752739385855</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.09478406787128581</v>
+        <v>0.2662414846031259</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.08264378139658068</v>
+        <v>-0.1922051192979058</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.2097814912168157</v>
+        <v>0.4454378253491029</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.4298113094000123</v>
+        <v>-0.1582150102843615</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.187017479986753</v>
+        <v>0.6211564877964508</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.1268809698977618</v>
+        <v>-0.07500969632701404</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.10016873743549</v>
+        <v>-0.04903096075406865</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.7126758857978428</v>
+        <v>0.1684462092059837</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.4746050493112844</v>
+        <v>-0.1861251020770899</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
@@ -3658,58 +3659,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.3739350848273759</v>
+        <v>0.3611104140957784</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.3042676360360523</v>
+        <v>0.4977561053218973</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.3816212997058295</v>
+        <v>-0.340159926303204</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1282330145072259</v>
+        <v>0.1055616243378702</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.2029190381317474</v>
+        <v>0.1506222500298758</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9324127906976745</v>
+        <v>0.9462007764836384</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.3816212997058296</v>
+        <v>-0.2306884935745911</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.2454989420305418</v>
+        <v>0.4536110241335325</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.7579231117208002</v>
+        <v>0.4900359107717698</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.3816212997058295</v>
+        <v>-0.340159926303204</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>1.221834426337418</v>
+        <v>0.7692578399355443</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>0.04718486063882166</v>
+        <v>0.03036925316019734</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>1.089249552232983</v>
+        <v>1.072718729465235</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.1240889646699911</v>
+        <v>-0.1156623821440808</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.0731435395633202</v>
+        <v>0.02380859098261445</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.1121597278185764</v>
+        <v>0.02770720757571521</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.03508146112409927</v>
+        <v>-0.003793509050400767</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -3958,28 +3959,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.02340987064093225</v>
+        <v>0.05341499464255506</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286764</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.08126757478702572</v>
+        <v>0.2216991067360366</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2145128387962868</v>
+        <v>0.2389480542019927</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.9832848837209303</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.1954368693665691</v>
+        <v>-0.5035092528573126</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -3988,10 +3989,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286764</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2720069211165614</v>
+        <v>1.12172130237064</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -4000,7 +4001,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.03286068493604632</v>
+        <v>-0.1530343433756415</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -4046,49 +4047,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.02427859728711668</v>
+        <v>0.2802901328432288</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.0008488550590588506</v>
+        <v>0.21537109245123</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.04278454166173134</v>
+        <v>0.1663071666219633</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1644125150610335</v>
+        <v>0.2118385751587301</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9241379310344827</v>
+        <v>0.9462209302325582</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.4439839127181155</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.07145768887935322</v>
+        <v>0.1198921439760285</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.7058271448015913</v>
+        <v>0.8817790541059516</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.4439839127181154</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.1881819355445027</v>
+        <v>1.302613471315189</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.06589978732071489</v>
+        <v>0.08525727141563522</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.6918277475147857</v>
+        <v>1.16126302367821</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.1240889646699911</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -4148,67 +4149,67 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.0298093061781104</v>
+        <v>0.1006115993414891</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.006253052389626035</v>
+        <v>0.04480342973943419</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.1410541034597298</v>
+        <v>-0.1506103472912015</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.04245763481668412</v>
+        <v>0.04829288677382208</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1639310826911156</v>
+        <v>0.07724581697211373</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.8758620689655172</v>
+        <v>0.3466569767441861</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.133289881480832</v>
+        <v>0.02220992715952153</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.07724314664631593</v>
+        <v>1.058870045499049</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.6820099089431698</v>
+        <v>-0.04411026616389809</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.1410541034597298</v>
+        <v>0</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.1881819355445027</v>
+        <v>0.07669821051320369</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.06589978732071489</v>
+        <v>-0.4925355138254077</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.6918277475147857</v>
+        <v>0.06837546042061436</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.1506103472912013</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.00539961384104104</v>
+        <v>-0.1403420434887794</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.00539961384104104</v>
+        <v>0.8384538694854164</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0</v>
+        <v>-0.532401671437185</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
       <c r="AE4" s="2" t="n">
-        <v>0.1656098075061709</v>
+        <v>0.1241816912769598</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>-0.1340945703114591</v>
+        <v>-0.08939590726649083</v>
       </c>
     </row>
     <row r="5">
@@ -4254,67 +4255,67 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.02279446582962819</v>
+        <v>0.3767591451106707</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.0006013278051721915</v>
+        <v>0.306948498087245</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.04297635660365116</v>
+        <v>0.1170715483255394</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.164545871413997</v>
+        <v>0.2012418815986788</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.9241379310344827</v>
+        <v>0.9280523255813954</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.1391937251083381</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.06990519713965893</v>
+        <v>0.2739414126958895</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.7122183524504826</v>
+        <v>0.7298771057515232</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.1881819355445027</v>
+        <v>1.176693874504713</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.06589978732071489</v>
+        <v>0.02590942178534528</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.6918277475147857</v>
+        <v>1.049007335438753</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.1240889646699911</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.001448952913220447</v>
+        <v>0.07534933667980903</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>-0.001448952913220558</v>
+        <v>0.1375572366932849</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0</v>
+        <v>-0.05468551208403816</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
       <c r="AE5" s="2" t="n">
-        <v>0.1656098075061709</v>
+        <v>0.1241816912769598</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>0.009509211625454705</v>
+        <v>0.01312838014984941</v>
       </c>
     </row>
     <row r="6">
@@ -4360,58 +4361,58 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.05929390134432888</v>
+        <v>0.2548427792228856</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.08081197412476204</v>
+        <v>0.1912140852415709</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.2697487878045376</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.06505625151393715</v>
+        <v>0.07755375275567253</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1446920916972296</v>
+        <v>0.1316538674840658</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9793103448275862</v>
+        <v>0.9447674418604651</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.2697487878045377</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.07145768887935322</v>
+        <v>0.4708254210135241</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.7058271448015913</v>
+        <v>0.5357374989114265</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.2697487878045376</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.09123630625457757</v>
+        <v>0.7183713744894256</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.142114489992951</v>
+        <v>-0.1901050469873418</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.3354190616917451</v>
+        <v>0.6404187679873986</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.005137027073558564</v>
+        <v>-0.1506103472912023</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.08159156976704773</v>
+        <v>-0.01987623974249531</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0</v>
+        <v>0.3133634599770951</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.08159156976704773</v>
+        <v>-0.2537299916394827</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
@@ -4462,58 +4463,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.01405857042339642</v>
+        <v>0.3346239523638623</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.009137394982988933</v>
+        <v>0.2669498337801117</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.4000942896051511</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.04425890301470417</v>
+        <v>0.1337899294054988</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1618643459723566</v>
+        <v>0.2052979460801001</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9586206896551724</v>
+        <v>0.9382267441860465</v>
       </c>
       <c r="P7" t="b">
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.4000942896051513</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.07145768887935322</v>
+        <v>0.2082918238603966</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.7058271448015913</v>
+        <v>0.7946115932025033</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.4000942896051511</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.176326517172573</v>
+        <v>1.224722867674378</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.07522003407025546</v>
+        <v>0.04854622762596184</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.6482427595914475</v>
+        <v>1.091824560241528</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.02015312857781404</v>
+        <v>-0.1240889646699911</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.009977780352717347</v>
+        <v>0.04243867708327231</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0</v>
+        <v>0.07893588713866384</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.009977780352717458</v>
+        <v>-0.03382704245029977</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -4564,58 +4565,58 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.0592939013443291</v>
+        <v>0.1520450866852068</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.08081197412476226</v>
+        <v>0.09362890460479822</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.1410541034597296</v>
+        <v>-0.1268809698977617</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.06505625151393719</v>
+        <v>0.05975876723144954</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.1446920916972295</v>
+        <v>0.1055520961703095</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9793103448275862</v>
+        <v>0.9680232558139535</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.1379446474939672</v>
+        <v>-0.04772465519664792</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.071457688879353</v>
+        <v>0.91801226968219</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.7058271448015918</v>
+        <v>0.09478406787128581</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.1410541034597296</v>
+        <v>-0.08264378139658068</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.09123630625457735</v>
+        <v>0.2097814912168157</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.1421144899929511</v>
+        <v>-0.4298113094000123</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.3354190616917443</v>
+        <v>0.187017479986753</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.005137027073558564</v>
+        <v>-0.1268809698977618</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.08159156976704796</v>
+        <v>-0.10016873743549</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>0.7126758857978428</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.08159156976704796</v>
+        <v>-0.4746050493112844</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
@@ -4666,58 +4667,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.01405857042339642</v>
+        <v>0.3739350848273759</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.009137394982988933</v>
+        <v>0.3042676360360523</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.3816212997058295</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.04425890301470417</v>
+        <v>0.1282330145072259</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1618643459723566</v>
+        <v>0.2029190381317474</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9586206896551724</v>
+        <v>0.9324127906976745</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.1379446474939671</v>
+        <v>-0.3816212997058296</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.07145768887935322</v>
+        <v>0.2454989420305418</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.7058271448015913</v>
+        <v>0.7579231117208002</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1410541034597297</v>
+        <v>-0.3816212997058295</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.176326517172573</v>
+        <v>1.221834426337418</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.07522003407025546</v>
+        <v>0.04718486063882166</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.6482427595914475</v>
+        <v>1.089249552232983</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.02015312857781404</v>
+        <v>-0.1240889646699911</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.009977780352717347</v>
+        <v>0.0731435395633202</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0</v>
+        <v>0.1121597278185764</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.009977780352717458</v>
+        <v>-0.03508146112409927</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -4966,28 +4967,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.09782647207714512</v>
+        <v>0.0189121018756262</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.2022979914860072</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1130717188570335</v>
+        <v>0.0809929380075199</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.4590501973559848</v>
+        <v>0.2138559415886582</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9098360655737705</v>
+        <v>0.9657534246575342</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.1989728318606708</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -4996,10 +4997,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.2022979914860072</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5467128924473776</v>
+        <v>0.2720069211165614</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -5008,7 +5009,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.0518515658788602</v>
+        <v>-0.03286068493604632</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -5054,49 +5055,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.007037250069187984</v>
+        <v>0.02497427700722055</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.08269906430310359</v>
+        <v>0.005949654656603798</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1167974844615735</v>
+        <v>0.04263876767180749</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.4296396949184721</v>
+        <v>0.1638459834801125</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>0.9178082191780822</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1373591481699221</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-3.784557661268284e-05</v>
+        <v>0.07691834452240665</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1.000092557658176</v>
+        <v>0.6903412233993171</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.418854880877529</v>
+        <v>0.1881819355445027</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.08266434720637639</v>
+        <v>-0.06589978732071489</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.7661331690981564</v>
+        <v>0.6918277475147857</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.07820336667939509</v>
+        <v>-0.02330447460112961</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -5156,64 +5157,68 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0.2241399968958406</v>
+        <v>0.0298970904328042</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.2932762846971693</v>
+        <v>0.01078109538296457</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.290246477182812</v>
+        <v>-0.1410541034597298</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.2118873802483123</v>
+        <v>0.04231297465229837</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.3766351040867174</v>
+        <v>0.1633648978332561</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1</v>
+        <v>0.8698630136986302</v>
       </c>
       <c r="P4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.290246477182812</v>
+        <v>-0.1332160003250361</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-3.784557661279386e-05</v>
+        <v>0.08209063830928276</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>1.000092557658176</v>
+        <v>0.6695185422013774</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.290246477182812</v>
+        <v>-0.1410541034597298</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.09314005237279877</v>
+        <v>0.1881819355445027</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.2932495373183879</v>
+        <v>-0.06589978732071489</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.170363738736532</v>
+        <v>0.6918277475147857</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.05160411514521168</v>
+        <v>-0.02330447460112961</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.2295617634294518</v>
+        <v>0.004802865336247741</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>0.004802865336247963</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.2295617634294517</v>
+        <v>0</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="n">
+        <v>0.1648186743793927</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>-0.1335803124522462</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5258,64 +5263,68 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.01033194945437088</v>
+        <v>0.02513250102906106</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.09852050782385913</v>
+        <v>0.006104941870828995</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.1248781540722552</v>
+        <v>0.04282992906858404</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.4262985277848752</v>
+        <v>0.1640013187009608</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1</v>
+        <v>0.9178082191780822</v>
       </c>
       <c r="P5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1372259833597972</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-3.784557661268284e-05</v>
+        <v>0.07708458708623156</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>1.000092557658176</v>
+        <v>0.6896719621294258</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.3943827240439621</v>
+        <v>0.1881819355445027</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.09848638952144639</v>
+        <v>-0.06589978732071489</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.721370813624854</v>
+        <v>0.6918277475147857</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.08544765322886083</v>
+        <v>-0.02330447460112961</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.01724782228499044</v>
+        <v>0.0001543687733340793</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0</v>
+        <v>0.0001543687733340793</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.01724782228499044</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="inlineStr"/>
-      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="n">
+        <v>0.1648186743793927</v>
+      </c>
+      <c r="AF5" s="2" t="n">
+        <v>0.0078908934314732</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5360,58 +5369,58 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0.2241399968958404</v>
+        <v>-0.05865498322464358</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.293276284697169</v>
+        <v>-0.07612735677344817</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.2118873802483122</v>
+        <v>0.06483459413525924</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.3766351040867174</v>
+        <v>0.1441995387797093</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1</v>
+        <v>0.9726027397260274</v>
       </c>
       <c r="P6" t="b">
         <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1373591481699221</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-3.784557661268284e-05</v>
+        <v>0.07691834452240665</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.000092557658176</v>
+        <v>0.6903412233993171</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.09314005237279877</v>
+        <v>0.09123630625457757</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.2932495373183879</v>
+        <v>-0.142114489992951</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.170363738736532</v>
+        <v>0.3354190616917451</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.05160411514521168</v>
+        <v>-0.005137027073558564</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>-0.2295617634294516</v>
+        <v>-0.08159156976704796</v>
       </c>
       <c r="Z6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.2295617634294517</v>
+        <v>-0.08159156976704773</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
@@ -5462,58 +5471,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.01033194945437088</v>
+        <v>0.01474730880405706</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.09852050782385913</v>
+        <v>-0.004087490043451769</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1248781540722552</v>
+        <v>0.04410810563248337</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.4262985277848752</v>
+        <v>0.1613070438482246</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1</v>
+        <v>0.952054794520548</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1373591481699221</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-3.784557661268284e-05</v>
+        <v>0.07691834452240665</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1.000092557658176</v>
+        <v>0.6903412233993171</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.3943827240439621</v>
+        <v>0.176326517172573</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.09848638952144639</v>
+        <v>-0.07522003407025546</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.721370813624854</v>
+        <v>0.6482427595914475</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.08544765322886083</v>
+        <v>-0.02015312857781404</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.01724782228499044</v>
+        <v>-0.009977780352717569</v>
       </c>
       <c r="Z7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.01724782228499044</v>
+        <v>-0.009977780352717458</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -5564,58 +5573,58 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0.2241399968958403</v>
+        <v>-0.0586549832246438</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.2932762846971689</v>
+        <v>-0.0761273567734484</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.2902464771828118</v>
+        <v>-0.1410541034597297</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.2118873802483121</v>
+        <v>0.06483459413525945</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.3766351040867174</v>
+        <v>0.1441995387797092</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1</v>
+        <v>0.9726027397260274</v>
       </c>
       <c r="P8" t="b">
         <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.2902464771828118</v>
+        <v>-0.1373591481699222</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-3.78455766124608e-05</v>
+        <v>0.07691834452240665</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.000092557658175</v>
+        <v>0.6903412233993177</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>-0.2902464771828118</v>
+        <v>-0.1410541034597297</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.09314005237279899</v>
+        <v>0.09123630625457735</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.2932495373183877</v>
+        <v>-0.1421144899929511</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.1703637387365324</v>
+        <v>0.3354190616917443</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.05160411514521168</v>
+        <v>-0.005137027073558564</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>-0.2295617634294514</v>
+        <v>-0.08159156976704818</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.2295617634294516</v>
+        <v>-0.08159156976704796</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
@@ -5666,58 +5675,58 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.01033194945437088</v>
+        <v>0.01474730880405706</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.09852050782385913</v>
+        <v>-0.004087490043451769</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.1248781540722552</v>
+        <v>0.04410810563248337</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.4262985277848752</v>
+        <v>0.1613070438482246</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>1</v>
+        <v>0.952054794520548</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1373591481699221</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>-3.784557661268284e-05</v>
+        <v>0.07691834452240665</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1.000092557658176</v>
+        <v>0.6903412233993171</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1410541034597296</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.3943827240439621</v>
+        <v>0.176326517172573</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.09848638952144639</v>
+        <v>-0.07522003407025546</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.721370813624854</v>
+        <v>0.6482427595914475</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.08544765322886083</v>
+        <v>-0.02015312857781404</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.01724782228499044</v>
+        <v>-0.009977780352717569</v>
       </c>
       <c r="Z9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.01724782228499044</v>
+        <v>-0.009977780352717458</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
@@ -5966,28 +5975,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>0.06101703543393833</v>
+        <v>0.1113578145363061</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.3239608533428744</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.179974191375289</v>
+        <v>0.1112768582964018</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.240579627043532</v>
+        <v>0.451830499217423</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.9746588693957114</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.3098313187450096</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -5996,10 +6005,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.3098313187450098</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.5373300241683001</v>
+        <v>0.5657770181230009</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -6008,7 +6017,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.1055402030174765</v>
+        <v>-0.0518515658788602</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -6054,49 +6063,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.06128603667882748</v>
+        <v>0.009125074064342265</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.0002535315041187758</v>
+        <v>-0.09198904181424106</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.1145251377344681</v>
+        <v>0.1149439295311541</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1732872931401137</v>
+        <v>0.4227552867946717</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.9649122807017544</v>
+        <v>0.9841269841269841</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.237660847618366</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.1045693220900867</v>
+        <v>-3.784557661268284e-05</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.7670652811375739</v>
+        <v>1.000092557658176</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.2376608476183659</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.3921442095204601</v>
+        <v>0.4217964992394458</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.09444023883315877</v>
+        <v>-0.09195467631537591</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.7298014104598676</v>
+        <v>0.7455172015271687</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.07741687217408433</v>
+        <v>-0.07820336667939509</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -6156,68 +6165,64 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0.03396006753160985</v>
+        <v>-0.2241272016883183</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.0895151536626404</v>
+        <v>-0.3018694895888229</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.2093348703683601</v>
+        <v>-0.290246477182812</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.1087073838403099</v>
+        <v>0.2122838060691882</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1474926725482544</v>
+        <v>0.3706057127778931</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.8791423001949318</v>
+        <v>1</v>
       </c>
       <c r="P4" t="b">
         <v>0</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-0.2055463545127731</v>
+        <v>-0.290246477182812</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.1511006904031149</v>
+        <v>-3.784557661279386e-05</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.6634137418558945</v>
+        <v>1.000092557658176</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>-0.2093348703683601</v>
+        <v>-0.290246477182812</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.2159802374321436</v>
+        <v>0.0931580800501699</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.2090311004691446</v>
+        <v>-0.3018430674371438</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.4019508081024246</v>
+        <v>0.1646551151180149</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-0.07741687217408399</v>
+        <v>-0.05160411514521168</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>-0.08974593174569512</v>
+        <v>-0.2311430780460305</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.04212625444366003</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.1265414681062376</v>
+        <v>-0.2311430780460303</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="n">
-        <v>0.678953431147129</v>
-      </c>
-      <c r="AF4" s="2" t="n">
-        <v>-0.4035884689523094</v>
-      </c>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6262,19 +6267,19 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.001898460228708654</v>
+        <v>-0.007673102214340366</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.05929734732007919</v>
+        <v>-0.107104044434429</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.2378794616385039</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.125484862997163</v>
+        <v>0.1229158402218673</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1697461539198723</v>
+        <v>0.4195376839827943</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>1</v>
@@ -6283,47 +6288,43 @@
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.237879461638504</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.1042525676124126</v>
+        <v>-3.784557661268284e-05</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.7677708715892542</v>
+        <v>1.000092557658176</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.2378794616385039</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.3096373730028814</v>
+        <v>0.3981288797931819</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.1481091552144772</v>
+        <v>-0.1070702509932032</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.576251761628526</v>
+        <v>0.7036851392691741</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.09585156482023383</v>
+        <v>-0.08544765322886083</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.05953578462717246</v>
+        <v>-0.01664627776121597</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>-0.0002867674045797797</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.05926601278325838</v>
+        <v>-0.01664627776121574</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="n">
-        <v>0.678953431147129</v>
-      </c>
-      <c r="AF5" s="2" t="n">
-        <v>-0.04772872481844626</v>
-      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6368,58 +6369,58 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.1756491859378704</v>
+        <v>-0.2241272016883182</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.1080398774719478</v>
+        <v>-0.3018694895888229</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.1215847395419751</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.03482783726599165</v>
+        <v>0.2122838060691881</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.08867046039686673</v>
+        <v>0.3706057127778931</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.9103313840155945</v>
+        <v>1</v>
       </c>
       <c r="P6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>-0.03144317402540209</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.4033624710605406</v>
+        <v>-3.784557661268284e-05</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>0.101484814875283</v>
+        <v>1.000092557658176</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>-0.1215847395419751</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.2138153946258015</v>
+        <v>0.0931580800501699</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.210439283990125</v>
+        <v>-0.3018430674371438</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.3979219195070163</v>
+        <v>0.1646551151180149</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-0.07741687217408422</v>
+        <v>-0.05160411514521168</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.1077590256599712</v>
+        <v>-0.2311430780460304</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.2705064707075802</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1280965101712315</v>
+        <v>-0.2311430780460303</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
@@ -6470,58 +6471,58 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.02410497175343318</v>
+        <v>-0.007673102214340366</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.03478932236503507</v>
+        <v>-0.107104044434429</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.222104966978485</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.1188103428199329</v>
+        <v>0.1229158402218673</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1666505507231491</v>
+        <v>0.4195376839827943</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9902534113060428</v>
+        <v>1</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.2218461188431556</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.1274836171091729</v>
+        <v>-3.784557661268284e-05</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.7160222528237516</v>
+        <v>1.000092557658176</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.222104966978485</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.3160699914918432</v>
+        <v>0.3981288797931819</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1439248757248198</v>
+        <v>-0.1070702509932032</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.5882232097137479</v>
+        <v>0.7036851392691741</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.09083171626673225</v>
+        <v>-0.08544765322886083</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.03503397165362521</v>
+        <v>-0.01664627776121597</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.02074500401271973</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.05464535750561472</v>
+        <v>-0.01664627776121574</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
@@ -6572,68 +6573,64 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.1313460375688129</v>
+        <v>-0.2241272016883181</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.06628451738864993</v>
+        <v>-0.3018694895888228</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.07741687217408422</v>
+        <v>-0.2902464771828118</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.01276474919454059</v>
+        <v>0.212283806069188</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.04922436856579283</v>
+        <v>0.3706057127778931</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.2241715399610136</v>
+        <v>1</v>
       </c>
       <c r="P8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>0.01130377776197578</v>
+        <v>-0.2902464771828118</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.465299433644307</v>
+        <v>-3.78455766124608e-05</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.036483651193696</v>
+        <v>1.000092557658175</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>0</v>
+        <v>-0.2902464771828118</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.1187004957822777</v>
+        <v>0.0931580800501699</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.2723094727903348</v>
+        <v>-0.3018430674371438</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.2209079903286753</v>
+        <v>0.1646551151180149</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-0.07741687217408433</v>
+        <v>-0.05160411514521168</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.0660142491926401</v>
+        <v>-0.2311430780460303</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.3265798753777083</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.196419100742712</v>
+        <v>-0.2311430780460303</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr"/>
-      <c r="AE8" s="2" t="n">
-        <v>0.09967003453281076</v>
-      </c>
-      <c r="AF8" s="2" t="n">
-        <v>-0.09051009422763445</v>
-      </c>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6678,68 +6675,64 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.006430108302580395</v>
+        <v>-0.007673102214340366</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.05144773863977858</v>
+        <v>-0.107104044434429</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.2217386103320992</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.120308212821147</v>
+        <v>0.1229158402218673</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1643805444217967</v>
+        <v>0.4195376839827943</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.9980506822612085</v>
+        <v>1</v>
       </c>
       <c r="P9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.2214796402899176</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.1280146156363324</v>
+        <v>-3.784557661268284e-05</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.7148394203240468</v>
+        <v>1.000092557658176</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.2217386103320992</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.2927473196428292</v>
+        <v>0.3981288797931819</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1590957703813733</v>
+        <v>-0.1070702509932032</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.5448184662600134</v>
+        <v>0.7036851392691741</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.09083171626673225</v>
+        <v>-0.08544765322886083</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.05168816556553635</v>
+        <v>-0.01664627776121597</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.02122573303220299</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.07139841490406329</v>
+        <v>-0.01664627776121574</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="n">
-        <v>0.09967003453281076</v>
-      </c>
-      <c r="AF9" s="2" t="n">
-        <v>-0.001640172913999871</v>
-      </c>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6982,28 +6975,28 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>-0.002396027003974344</v>
+        <v>0.06101703543393833</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428744</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.1038210158252791</v>
+        <v>0.179974191375289</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.3353086213005002</v>
+        <v>0.240579627043532</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1</v>
+        <v>0.9746588693957114</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-0.2242012270138072</v>
+        <v>-0.3098313187450096</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>0</v>
@@ -7012,10 +7005,10 @@
         <v>1</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3098313187450098</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.2859055823922787</v>
+        <v>0.5373300241683001</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>0</v>
@@ -7024,7 +7017,7 @@
         <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-0.07899825662835758</v>
+        <v>-0.1055402030174765</v>
       </c>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -7070,49 +7063,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>-0.04586689094251117</v>
+        <v>0.06128603667882748</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.04357527146567408</v>
+        <v>0.0002535315041187758</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.07490796810752959</v>
+        <v>0.1145251377344681</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.233580415802233</v>
+        <v>0.1732872931401137</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1</v>
+        <v>0.9649122807017544</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.237660847618366</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.0903287250712983</v>
+        <v>0.1045693220900867</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.6874374194597751</v>
+        <v>0.7670652811375739</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>-0.1541243129380868</v>
+        <v>-0.2376608476183659</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0.1279826618159459</v>
+        <v>0.3921442095204601</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>-0.1228106656808624</v>
+        <v>-0.09444023883315877</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.4476396044633588</v>
+        <v>0.7298014104598676</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.07741687217408433</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0</v>
@@ -7172,67 +7165,67 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>-0.03396006753160985</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.01733422320252109</v>
+        <v>-0.0895151536626404</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>-0.2093348703683601</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0</v>
+        <v>0.1087073838403099</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.1474926725482544</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0</v>
+        <v>0.8791423001949318</v>
       </c>
       <c r="P4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.2055463545127731</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.1511006904031149</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>0.6634137418558945</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0</v>
+        <v>-0.2093348703683601</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.2159802374321436</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>-0.2152266720452527</v>
+        <v>-0.2090311004691446</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.03198399714010956</v>
+        <v>0.4019508081024246</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0</v>
+        <v>-0.07741687217408399</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.06368456696172653</v>
+        <v>-0.08974593174569512</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.1889455515140797</v>
+        <v>0.04212625444366003</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>-0.1053546854124969</v>
+        <v>-0.1265414681062376</v>
       </c>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr"/>
       <c r="AE4" s="2" t="n">
-        <v>0.10904401508735</v>
+        <v>0.678953431147129</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>-0.08356097205346547</v>
+        <v>-0.4035884689523094</v>
       </c>
     </row>
     <row r="5">
@@ -7278,19 +7271,19 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0.05204807535905154</v>
+        <v>-0.001898460228708654</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.04977130173806454</v>
+        <v>-0.05929734732007919</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.1245530606971789</v>
+        <v>-0.2378794616385039</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.06536837225202972</v>
+        <v>0.125484862997163</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.216177540659731</v>
+        <v>0.1697461539198723</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>1</v>
@@ -7299,46 +7292,46 @@
         <v>0</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-0.1245530606971789</v>
+        <v>-0.237879461638504</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.1284458931702923</v>
+        <v>0.1042525676124126</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.5555413873337472</v>
+        <v>0.7677708715892542</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>-0.1245530606971789</v>
+        <v>-0.2378794616385039</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.08282053666881062</v>
+        <v>0.3096373730028814</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>-0.1579315375127712</v>
+        <v>-0.1481091552144772</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.289677927852336</v>
+        <v>0.576251761628526</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-0.04770979298828082</v>
+        <v>-0.09585156482023383</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>-0.006478325044863231</v>
+        <v>-0.05953578462717246</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.03495933586130318</v>
+        <v>-0.0002867674045797797</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>-0.04003796040129592</v>
+        <v>-0.05926601278325838</v>
       </c>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr"/>
       <c r="AE5" s="2" t="n">
-        <v>0.10904401508735</v>
+        <v>0.678953431147129</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>-0.03077953492302243</v>
+        <v>-0.04772872481844626</v>
       </c>
     </row>
     <row r="6">
@@ -7384,68 +7377,64 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>0.1756491859378704</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.01733422320252109</v>
+        <v>0.1080398774719478</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>-0.1215847395419751</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0</v>
+        <v>0.03482783726599165</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.08867046039686673</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0</v>
+        <v>0.9103313840155945</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>-0.03144317402540209</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.4033624710605406</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>0.101484814875283</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>0</v>
+        <v>-0.1215847395419751</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.2138153946258015</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>-0.2152266720452527</v>
+        <v>-0.210439283990125</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.03198399714010956</v>
+        <v>0.3979219195070163</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0</v>
+        <v>-0.07741687217408422</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.06368456696172653</v>
+        <v>0.1077590256599712</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.1889455515140797</v>
+        <v>0.2705064707075802</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>-0.1053546854124969</v>
+        <v>-0.1280965101712315</v>
       </c>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr"/>
-      <c r="AE6" s="2" t="n">
-        <v>0.06587707306593193</v>
-      </c>
-      <c r="AF6" s="2" t="n">
-        <v>-0.05707000491572445</v>
-      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7490,68 +7479,64 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0.05204807535905154</v>
+        <v>0.02410497175343318</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.04977130173806454</v>
+        <v>-0.03478932236503507</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.1245530606971789</v>
+        <v>-0.222104966978485</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0.06536837225202972</v>
+        <v>0.1188103428199329</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.216177540659731</v>
+        <v>0.1666505507231491</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1</v>
+        <v>0.9902534113060428</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>-0.1245530606971789</v>
+        <v>-0.2218461188431556</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.1284458931702923</v>
+        <v>0.1274836171091729</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.5555413873337472</v>
+        <v>0.7160222528237516</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>-0.1245530606971789</v>
+        <v>-0.222104966978485</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>0.08282053666881062</v>
+        <v>0.3160699914918432</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>-0.1579315375127712</v>
+        <v>-0.1439248757248198</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>0.289677927852336</v>
+        <v>0.5882232097137479</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>-0.04770979298828082</v>
+        <v>-0.09083171626673225</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>-0.006478325044863231</v>
+        <v>-0.03503397165362521</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.03495933586130318</v>
+        <v>0.02074500401271973</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>-0.04003796040129592</v>
+        <v>-0.05464535750561472</v>
       </c>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
-      <c r="AE7" s="2" t="n">
-        <v>0.06587707306593193</v>
-      </c>
-      <c r="AF7" s="2" t="n">
-        <v>0.002524249698548031</v>
-      </c>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7596,67 +7581,67 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.0148966629316607</v>
+        <v>0.1313460375688129</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.01733422320252109</v>
+        <v>0.06628451738864993</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>-0.07741687217408422</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0</v>
+        <v>0.01276474919454059</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1.757200726823261e-05</v>
+        <v>0.04922436856579283</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0</v>
+        <v>0.2241715399610136</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>0.005700135266177409</v>
+        <v>0.01130377776197578</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.296341487361538</v>
+        <v>0.465299433644307</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-0.02542419299884729</v>
+        <v>-0.036483651193696</v>
       </c>
       <c r="T8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>0.009144403329576001</v>
+        <v>0.1187004957822777</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>-0.2152266720452527</v>
+        <v>-0.2723094727903348</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>0.03198399714010956</v>
+        <v>0.2209079903286753</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>0</v>
+        <v>-0.07741687217408433</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.06368456696172653</v>
+        <v>0.0660142491926401</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.1889455515140797</v>
+        <v>0.3265798753777083</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>-0.1053546854124969</v>
+        <v>-0.196419100742712</v>
       </c>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr"/>
       <c r="AE8" s="2" t="n">
-        <v>0.10904401508735</v>
+        <v>0.09967003453281076</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>-0.08356097205346547</v>
+        <v>-0.09051009422763445</v>
       </c>
     </row>
     <row r="9">
@@ -7702,67 +7687,67 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0.05204807535905154</v>
+        <v>0.006430108302580395</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.04977130173806454</v>
+        <v>-0.05144773863977858</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-0.1245530606971789</v>
+        <v>-0.2217386103320992</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.06536837225202972</v>
+        <v>0.120308212821147</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.216177540659731</v>
+        <v>0.1643805444217967</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>1</v>
+        <v>0.9980506822612085</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.1245530606971789</v>
+        <v>-0.2214796402899176</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.1284458931702923</v>
+        <v>0.1280146156363324</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0.5555413873337472</v>
+        <v>0.7148394203240468</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>-0.1245530606971789</v>
+        <v>-0.2217386103320992</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>0.08282053666881062</v>
+        <v>0.2927473196428292</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>-0.1579315375127712</v>
+        <v>-0.1590957703813733</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.289677927852336</v>
+        <v>0.5448184662600134</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-0.04770979298828082</v>
+        <v>-0.09083171626673225</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>-0.006478325044863231</v>
+        <v>-0.05168816556553635</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.03495933586130318</v>
+        <v>0.02122573303220299</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>-0.04003796040129592</v>
+        <v>-0.07139841490406329</v>
       </c>
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr"/>
       <c r="AE9" s="2" t="n">
-        <v>0.10904401508735</v>
+        <v>0.09967003453281076</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>-0.03077953492302243</v>
+        <v>-0.001640172913999871</v>
       </c>
     </row>
   </sheetData>
@@ -7776,7 +7761,1031 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AF9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="19" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="17" customWidth="1" min="32" max="32"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>full_cum_return</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>full_excess_return</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>full_max_dd</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_ann_vol</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_underwater_share</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_recovered</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_cum_return</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_excess_return</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_down_capture</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cum_return</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_excess_return</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_recovery_capture</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_max_dd</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>0.004925019651873308</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0.1032426212645815</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>0.3336266559947872</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.9887640449438202</v>
+      </c>
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>-0.2242012270138072</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>0.2953423679490121</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>-0.07899825662835758</v>
+      </c>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AD2" s="2" t="inlineStr"/>
+      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>-0.04249523517146048</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>-0.04718785371645051</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0.07462520970126199</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.2323499724942579</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>0.0903287250712983</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>0.6874374194597751</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>-0.1541243129380868</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>0.1319686562387929</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>-0.1261239620911172</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>0.4468327966462841</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>-0.04910852885624428</v>
+      </c>
+      <c r="Y3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>-0.2208132840633974</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>0.03153481080418825</v>
+      </c>
+      <c r="X4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="2" t="n">
+        <v>0.06011669793408791</v>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>0.1889455515140797</v>
+      </c>
+      <c r="AA4" s="2" t="n">
+        <v>-0.1083555537223155</v>
+      </c>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="n">
+        <v>0.10904401508735</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>-0.08356097205346547</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>-0.05013310178608843</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>-0.05478828804265912</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>-0.1245530606971789</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>0.06521864695715721</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>0.2149911464478618</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>-0.1245530606971789</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0.1284458931702923</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>0.5555413873337472</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>-0.1245530606971789</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>0.08500796058565951</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>-0.1623774629532012</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>0.2878285332916924</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>-0.04770979298828082</v>
+      </c>
+      <c r="Y5" s="2" t="n">
+        <v>-0.007976844497474267</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>0.03495933586130318</v>
+      </c>
+      <c r="AA5" s="2" t="n">
+        <v>-0.04148586216969152</v>
+      </c>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="n">
+        <v>0.10904401508735</v>
+      </c>
+      <c r="AF5" s="2" t="n">
+        <v>-0.03077953492302243</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>-0.2208132840633974</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0.03153481080418825</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="2" t="n">
+        <v>0.06011669793408791</v>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>0.1889455515140797</v>
+      </c>
+      <c r="AA6" s="2" t="n">
+        <v>-0.1083555537223155</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="n">
+        <v>0.06587707306593193</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>-0.05707000491572445</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>-0.05013310178608843</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>-0.05478828804265912</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>-0.1245530606971789</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>0.06521864695715721</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0.2149911464478618</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>-0.1245530606971789</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0.1284458931702923</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>0.5555413873337472</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>-0.1245530606971789</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>0.08500796058565951</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>-0.1623774629532012</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0.2878285332916924</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>-0.04770979298828082</v>
+      </c>
+      <c r="Y7" s="2" t="n">
+        <v>-0.007976844497474267</v>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>0.03495933586130318</v>
+      </c>
+      <c r="AA7" s="2" t="n">
+        <v>-0.04148586216969152</v>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="n">
+        <v>0.06587707306593193</v>
+      </c>
+      <c r="AF7" s="2" t="n">
+        <v>0.002524249698548031</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>0.01506678954618668</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0.01009206626960757</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>1.748592107069762e-05</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0.005700135266177409</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>0.296341487361538</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>-0.02542419299884729</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>0.00931356569573305</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>-0.2208132840633974</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>0.03153481080418825</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="2" t="n">
+        <v>0.06011669793408791</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>0.1889455515140797</v>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v>-0.1083555537223155</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="n">
+        <v>0.10904401508735</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>-0.08356097205346547</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>-0.05013310178608843</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>-0.05478828804265912</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>-0.1245530606971789</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>0.06521864695715721</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>0.2149911464478618</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>-0.1245530606971789</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>0.1284458931702923</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>0.5555413873337472</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>-0.1245530606971789</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>0.08500796058565951</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>-0.1623774629532012</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>0.2878285332916924</v>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>-0.04770979298828082</v>
+      </c>
+      <c r="Y9" s="2" t="n">
+        <v>-0.007976844497474267</v>
+      </c>
+      <c r="Z9" s="2" t="n">
+        <v>0.03495933586130318</v>
+      </c>
+      <c r="AA9" s="2" t="n">
+        <v>-0.04148586216969152</v>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="n">
+        <v>0.10904401508735</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>-0.03077953492302243</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7882,24 +8891,22 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>373</v>
-      </c>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>23</v>
+      </c>
       <c r="J2" s="2" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.4111111111111111</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -7930,20 +8937,20 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-131</v>
+        <v>196</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>523</v>
+        <v>373</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>0.7281976744186046</v>
+        <v>0.473655019412091</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -7977,23 +8984,23 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-120</v>
+        <v>-131</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-57</v>
+        <v>523</v>
       </c>
       <c r="G4" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>0.04137931034482759</v>
+        <v>0.7281976744186046</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -8023,19 +9030,21 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="n">
+        <v>-119</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>-57</v>
+      </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="2" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.04794520547945205</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -8068,24 +9077,22 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>-442</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>-132</v>
-      </c>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="J6" s="2" t="n">
-        <v>0.3625730994152047</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -8116,21 +9123,23 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-94</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
+        <v>-442</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>-132</v>
+      </c>
       <c r="G7" t="n">
-        <v>94</v>
+        <v>442</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="2" t="n">
-        <v>1</v>
+        <v>0.3625730994152047</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -8147,37 +9156,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>259</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>59</v>
-      </c>
+        <v>-94</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="2" t="n">
-        <v>0.1058171745152355</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
@@ -8204,27 +9211,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>-43</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>23</v>
+      </c>
       <c r="J9" s="2" t="n">
-        <v>0.3204941860465116</v>
+        <v>0.4111111111111111</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -8251,25 +9256,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>258</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>59</v>
+      </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="2" t="n">
+        <v>0.1059345535219079</v>
+      </c>
+      <c r="K10" t="n">
         <v>6</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.4206896551724138</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -8296,25 +9303,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-43</v>
+      </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="2" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.3204941860465116</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -8341,24 +9350,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>119</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr"/>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="J12" s="2" t="n">
-        <v>0.4892787524366471</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
@@ -8388,27 +9395,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>-30</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>58</v>
-      </c>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="J13" s="2" t="n">
-        <v>1</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>2</v>
@@ -8425,24 +9430,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>183</v>
+        <v>119</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -8452,10 +9457,10 @@
       </c>
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="2" t="n">
-        <v>0.313573407202216</v>
+        <v>0.4892787524366471</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -8472,37 +9477,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>59</v>
+        <v>-30</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
       </c>
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="2" t="n">
-        <v>0.4585755813953488</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -8529,25 +9534,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr"/>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>339</v>
+      </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="2" t="n">
-        <v>0.4206896551724138</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -8574,25 +9581,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>183</v>
+      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="b">
-        <v>1</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="2" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.3139212423738214</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -8619,27 +9628,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>-63</v>
+        <v>59</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="G18" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="2" t="n">
-        <v>0.7309941520467836</v>
+        <v>0.4585755813953488</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -8666,32 +9675,169 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>-94</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>58</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="J19" s="2" t="n">
-        <v>1</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-63</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="G21" t="n">
+        <v>63</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="2" t="n">
+        <v>0.7309941520467836</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>-94</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="G22" t="n">
+        <v>94</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
